--- a/data/_general_data/diets/all_ingredients.xlsx
+++ b/data/_general_data/diets/all_ingredients.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\treimer\Documents\R-temp-files\local_to_global_mariculture_modelling\data\_general_data\diets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45BAF6E-9BFF-4196-AEB1-42FD8CFC7554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{291D5FC5-1FC6-4A72-819B-3911202AA841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4656" yWindow="0" windowWidth="30432" windowHeight="16656" activeTab="2" xr2:uid="{EACE1C46-B374-4940-8FA1-58EDCA6D9B2B}"/>
+    <workbookView xWindow="348" yWindow="1272" windowWidth="20148" windowHeight="14988" activeTab="3" xr2:uid="{EACE1C46-B374-4940-8FA1-58EDCA6D9B2B}"/>
   </bookViews>
   <sheets>
     <sheet name="all_ingredients" sheetId="2" r:id="rId1"/>
@@ -19,13 +19,13 @@
     <sheet name="sources" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">all_ingredients!$A$1:$S$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">all_ingredients!$A$1:$S$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">not_in_use!$A$1:$S$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">sources!$A$1:$D$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="145">
   <si>
     <t>ingredient</t>
   </si>
@@ -241,15 +241,6 @@
     <t>Fish meal, 60-68% protein as fed | Feedipedia</t>
   </si>
   <si>
-    <t>yellow-highlight</t>
-  </si>
-  <si>
-    <t>All yellow-highlighted cells are taken from Louise's results!</t>
-  </si>
-  <si>
-    <t>grey-highlight</t>
-  </si>
-  <si>
     <t>All grey-highlighted cells are placeholder values</t>
   </si>
   <si>
@@ -476,6 +467,18 @@
   </si>
   <si>
     <t>PROTEIN</t>
+  </si>
+  <si>
+    <t>insect-meal</t>
+  </si>
+  <si>
+    <t>All yellow-highlighted cells are taken from Louise's results</t>
+  </si>
+  <si>
+    <t>aa-yellow-highlight</t>
+  </si>
+  <si>
+    <t>aa-grey-highlight</t>
   </si>
 </sst>
 </file>
@@ -484,7 +487,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="171" formatCode="0.0000%"/>
+    <numFmt numFmtId="165" formatCode="0.0000%"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -997,7 +1000,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1016,11 +1019,10 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="34" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="36" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="44">
@@ -1106,7 +1108,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Tormey Reimer" refreshedDate="46078.437356712966" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="27" xr:uid="{6D4F782E-02BC-4637-8610-FB6EA4233406}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:S28" sheet="all_ingredients"/>
+    <worksheetSource ref="A1:S29" sheet="all_ingredients"/>
   </cacheSource>
   <cacheFields count="19">
     <cacheField name="ingredient" numFmtId="0">
@@ -1778,7 +1780,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9BFEF1C-3877-4974-B792-0D846C532E8F}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9BFEF1C-3877-4974-B792-0D846C532E8F}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B3:H30" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
     <pivotField axis="axisRow" showAll="0" nonAutoSortDefault="1">
@@ -2283,13 +2285,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEB86C80-6855-4296-9746-1E92B0D65FFA}">
-  <dimension ref="A1:S53"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.6640625" customWidth="1"/>
     <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="9" width="12" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
@@ -2301,16 +2303,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>43</v>
@@ -2325,7 +2327,7 @@
         <v>45</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>40</v>
@@ -2357,195 +2359,193 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F2" s="8">
-        <v>0</v>
-      </c>
-      <c r="G2" s="8">
-        <v>1</v>
-      </c>
-      <c r="H2" s="8">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="F2" s="9">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="G2" s="9">
+        <v>0.224</v>
+      </c>
+      <c r="H2" s="10">
+        <f>1-SUM(F2:G2,I2)</f>
+        <v>0.11099999999999999</v>
       </c>
       <c r="I2" s="8">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="J2" s="12">
         <f>SUM(F2:I2)</f>
         <v>1</v>
       </c>
-      <c r="K2" s="8">
-        <v>0</v>
-      </c>
-      <c r="L2" s="8">
-        <f>K2*0.95</f>
-        <v>0</v>
-      </c>
-      <c r="M2" s="8">
-        <f>L2*1.05</f>
-        <v>0</v>
-      </c>
-      <c r="N2" s="8">
-        <v>0.95176181599999998</v>
-      </c>
-      <c r="O2" s="8">
-        <f>N2*0.95</f>
-        <v>0.90417372519999994</v>
-      </c>
-      <c r="P2" s="8">
-        <f>N2*1.05</f>
-        <v>0.99934990680000002</v>
+      <c r="K2" s="9">
+        <v>0.81859999999999999</v>
+      </c>
+      <c r="L2" s="9">
+        <v>0.71939999999999993</v>
+      </c>
+      <c r="M2" s="9">
+        <v>0.88099999999999989</v>
+      </c>
+      <c r="N2" s="9">
+        <v>0.95640000000000003</v>
+      </c>
+      <c r="O2" s="9">
+        <v>0.9466</v>
+      </c>
+      <c r="P2" s="9">
+        <v>0.96530000000000005</v>
       </c>
       <c r="Q2" s="8">
-        <v>0</v>
+        <v>0.41000000000000003</v>
       </c>
       <c r="R2" s="10">
         <f>Q2*0.95</f>
-        <v>0</v>
+        <v>0.38950000000000001</v>
       </c>
       <c r="S2" s="10">
         <f>R2*1.05</f>
-        <v>0</v>
+        <v>0.40897500000000003</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F3" s="8">
-        <v>0</v>
-      </c>
-      <c r="G3" s="8">
-        <v>0</v>
-      </c>
-      <c r="H3" s="8">
-        <v>0</v>
-      </c>
-      <c r="I3" s="8">
-        <v>1</v>
+        <v>68</v>
+      </c>
+      <c r="F3" s="9">
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="G3" s="9">
+        <v>0.13</v>
+      </c>
+      <c r="H3" s="10">
+        <f>1-SUM(F3:G3,I3)</f>
+        <v>0.46672719298245613</v>
+      </c>
+      <c r="I3" s="11">
+        <v>7.6272807017543895E-2</v>
       </c>
       <c r="J3" s="12">
         <f>SUM(F3:I3)</f>
         <v>1</v>
       </c>
-      <c r="K3" s="8">
-        <v>0</v>
-      </c>
-      <c r="L3" s="8">
-        <v>0</v>
-      </c>
-      <c r="M3" s="8">
-        <v>0</v>
-      </c>
-      <c r="N3" s="8">
-        <v>0</v>
-      </c>
-      <c r="O3" s="8">
-        <f>N3*0.95</f>
-        <v>0</v>
-      </c>
-      <c r="P3" s="8">
-        <f>N3*1.05</f>
-        <v>0</v>
+      <c r="K3" s="9">
+        <v>0.91110000000000002</v>
+      </c>
+      <c r="L3" s="9">
+        <v>0.88849999999999996</v>
+      </c>
+      <c r="M3" s="9">
+        <v>0.93099999999999994</v>
+      </c>
+      <c r="N3" s="9">
+        <v>0.94319999999999993</v>
+      </c>
+      <c r="O3" s="9">
+        <v>0.91969999999999996</v>
+      </c>
+      <c r="P3" s="9">
+        <v>0.9667</v>
       </c>
       <c r="Q3" s="8">
-        <v>0</v>
+        <v>0.68600000000000005</v>
       </c>
       <c r="R3" s="10">
         <f>Q3*0.95</f>
-        <v>0</v>
+        <v>0.65170000000000006</v>
       </c>
       <c r="S3" s="10">
         <f>R3*1.05</f>
-        <v>0</v>
+        <v>0.68428500000000014</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" s="8">
-        <v>0</v>
-      </c>
-      <c r="G4" s="8">
-        <v>1</v>
-      </c>
-      <c r="H4" s="8">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="F4" s="9">
+        <v>0.86849038461538397</v>
+      </c>
+      <c r="G4" s="9">
+        <f>6.7799419/100</f>
+        <v>6.7799419E-2</v>
+      </c>
+      <c r="H4" s="10">
+        <f>1-SUM(F4:G4,I4)</f>
+        <v>1.3710196384616014E-2</v>
       </c>
       <c r="I4" s="8">
-        <v>0</v>
+        <f>5/100</f>
+        <v>0.05</v>
       </c>
       <c r="J4" s="12">
         <f>SUM(F4:I4)</f>
         <v>1</v>
       </c>
-      <c r="K4" s="8">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8">
-        <f>K4*0.95</f>
-        <v>0</v>
-      </c>
-      <c r="M4" s="8">
-        <f>L4*1.05</f>
-        <v>0</v>
-      </c>
-      <c r="N4" s="8">
-        <v>0.95176181599999998</v>
-      </c>
-      <c r="O4" s="8">
-        <f>N4*0.95</f>
-        <v>0.90417372519999994</v>
-      </c>
-      <c r="P4" s="8">
-        <f>N4*1.05</f>
-        <v>0.99934990680000002</v>
+      <c r="K4" s="9">
+        <v>0.86599999999999999</v>
+      </c>
+      <c r="L4" s="9">
+        <v>0.75829999999999997</v>
+      </c>
+      <c r="M4" s="9">
+        <v>0.94739999999999991</v>
+      </c>
+      <c r="N4" s="9">
+        <v>0.93709999999999993</v>
+      </c>
+      <c r="O4" s="9">
+        <v>0.87280000000000002</v>
+      </c>
+      <c r="P4" s="9">
+        <v>0.97950000000000004</v>
       </c>
       <c r="Q4" s="8">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="R4" s="10">
         <f>Q4*0.95</f>
-        <v>0</v>
+        <v>0.74099999999999999</v>
       </c>
       <c r="S4" s="10">
         <f>R4*1.05</f>
-        <v>0</v>
+        <v>0.77805000000000002</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -2553,16 +2553,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F5" s="9">
         <v>0.73424999999999996</v>
@@ -2583,22 +2583,22 @@
         <v>1</v>
       </c>
       <c r="K5" s="9">
-        <v>0.87984013184420995</v>
+        <v>0.87980000000000003</v>
       </c>
       <c r="L5" s="9">
-        <v>0.82968438947751899</v>
+        <v>0.82969999999999999</v>
       </c>
       <c r="M5" s="9">
-        <v>0.922123463912633</v>
+        <v>0.92209999999999992</v>
       </c>
       <c r="N5" s="9">
-        <v>0.95670948993092597</v>
+        <v>0.95669999999999999</v>
       </c>
       <c r="O5" s="9">
-        <v>0.89930858976900496</v>
+        <v>0.8993000000000001</v>
       </c>
       <c r="P5" s="9">
-        <v>0.99203085303952299</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="Q5" s="8">
         <f>83.3/100</f>
@@ -2618,16 +2618,16 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F6" s="9">
         <v>0.73424999999999996</v>
@@ -2648,22 +2648,22 @@
         <v>1</v>
       </c>
       <c r="K6" s="9">
-        <v>0.87984013184420995</v>
+        <v>0.87980000000000003</v>
       </c>
       <c r="L6" s="9">
-        <v>0.82968438947751899</v>
+        <v>0.82969999999999999</v>
       </c>
       <c r="M6" s="9">
-        <v>0.922123463912633</v>
+        <v>0.92209999999999992</v>
       </c>
       <c r="N6" s="9">
-        <v>0.95670948993092597</v>
+        <v>0.95669999999999999</v>
       </c>
       <c r="O6" s="9">
-        <v>0.89930858976900496</v>
+        <v>0.8993000000000001</v>
       </c>
       <c r="P6" s="9">
-        <v>0.99203085303952299</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="Q6" s="8">
         <f>81.7/100</f>
@@ -2680,641 +2680,619 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F7" s="8">
-        <v>0</v>
-      </c>
-      <c r="G7" s="8">
-        <v>1</v>
-      </c>
-      <c r="H7" s="8">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="F7" s="9">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="H7" s="10">
+        <f>1-SUM(F7:G7,I7)</f>
+        <v>0.1070000000000001</v>
       </c>
       <c r="I7" s="8">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="J7" s="12">
         <f>SUM(F7:I7)</f>
         <v>1</v>
       </c>
-      <c r="K7" s="8">
-        <v>0</v>
-      </c>
-      <c r="L7" s="8">
-        <f>K7*0.95</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="8">
-        <f>L7*1.05</f>
-        <v>0</v>
+      <c r="K7" s="9">
+        <v>0.88470000000000004</v>
+      </c>
+      <c r="L7" s="9">
+        <v>0.84920000000000007</v>
+      </c>
+      <c r="M7" s="9">
+        <v>0.93629999999999991</v>
       </c>
       <c r="N7" s="9">
-        <v>0.95670948993092597</v>
+        <v>0.9466</v>
       </c>
       <c r="O7" s="9">
-        <v>0.89930858976900496</v>
+        <v>0.91510000000000002</v>
       </c>
       <c r="P7" s="9">
-        <v>0.99203085303952299</v>
+        <v>0.97360000000000002</v>
       </c>
       <c r="Q7" s="8">
-        <v>0</v>
+        <v>0.41000000000000003</v>
       </c>
       <c r="R7" s="10">
         <f>Q7*0.95</f>
-        <v>0</v>
+        <v>0.38950000000000001</v>
       </c>
       <c r="S7" s="10">
         <f>R7*1.05</f>
-        <v>0</v>
+        <v>0.40897500000000003</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F8" s="8">
-        <v>0</v>
-      </c>
-      <c r="G8" s="8">
-        <v>1</v>
-      </c>
-      <c r="H8" s="8">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="F8" s="9">
+        <v>0.55099999999999993</v>
+      </c>
+      <c r="G8" s="9">
+        <f>26.92252/100</f>
+        <v>0.2692252</v>
+      </c>
+      <c r="H8" s="10">
+        <f>1-SUM(F8:G8,I8)</f>
+        <v>4.08748000000001E-2</v>
       </c>
       <c r="I8" s="8">
-        <v>0</v>
+        <f>13.89/100</f>
+        <v>0.1389</v>
       </c>
       <c r="J8" s="12">
         <f>SUM(F8:I8)</f>
         <v>1</v>
       </c>
-      <c r="K8" s="8">
-        <v>0</v>
-      </c>
-      <c r="L8" s="8">
-        <f>K8*0.95</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="8">
-        <f>L8*1.05</f>
-        <v>0</v>
+      <c r="K8" s="9">
+        <v>0.87769999999999992</v>
+      </c>
+      <c r="L8" s="9">
+        <v>0.86930000000000007</v>
+      </c>
+      <c r="M8" s="9">
+        <v>0.88549999999999995</v>
       </c>
       <c r="N8" s="9">
-        <v>0.95670948993092597</v>
+        <v>0.95109999999999995</v>
       </c>
       <c r="O8" s="9">
-        <v>0.89930858976900496</v>
+        <v>0.93889999999999996</v>
       </c>
       <c r="P8" s="9">
-        <v>0.99203085303952299</v>
+        <v>0.95739999999999992</v>
       </c>
       <c r="Q8" s="8">
-        <v>0</v>
-      </c>
-      <c r="R8" s="10">
-        <f>Q8*0.95</f>
-        <v>0</v>
-      </c>
-      <c r="S8" s="10">
-        <f>R8*1.05</f>
-        <v>0</v>
+        <v>0.59399999999999997</v>
+      </c>
+      <c r="R8" s="8">
+        <f>Q8-3*(2.16/100)</f>
+        <v>0.5292</v>
+      </c>
+      <c r="S8" s="8">
+        <f>Q8+3*(2.16/100)</f>
+        <v>0.65879999999999994</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E9" t="s">
-        <v>72</v>
-      </c>
-      <c r="F9" s="8">
-        <v>0.42</v>
-      </c>
-      <c r="G9" s="8">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="H9" s="8">
-        <v>0.46899999999999997</v>
+        <v>68</v>
+      </c>
+      <c r="F9" s="9">
+        <v>0.53783333333333327</v>
+      </c>
+      <c r="G9" s="9">
+        <f>13.249433/100</f>
+        <v>0.13249432999999999</v>
+      </c>
+      <c r="H9" s="10">
+        <f>1-SUM(F9:G9,I9)</f>
+        <v>2.4672336666666794E-2</v>
       </c>
       <c r="I9" s="8">
-        <v>5.8000000000000003E-2</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="J9" s="12">
         <f>SUM(F9:I9)</f>
         <v>1</v>
       </c>
-      <c r="K9" s="8">
-        <v>0.63000000000000012</v>
-      </c>
-      <c r="L9" s="13">
-        <f>K9*0.95</f>
-        <v>0.59850000000000003</v>
-      </c>
-      <c r="M9" s="13">
-        <f>L9*1.05</f>
-        <v>0.62842500000000001</v>
-      </c>
-      <c r="N9" s="8">
-        <v>0.95176181599999998</v>
-      </c>
-      <c r="O9" s="8">
-        <f>N9*0.95</f>
-        <v>0.90417372519999994</v>
-      </c>
-      <c r="P9" s="8">
-        <f>N9*1.05</f>
-        <v>0.99934990680000002</v>
+      <c r="K9" s="9">
+        <v>0.83030000000000004</v>
+      </c>
+      <c r="L9" s="9">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="M9" s="9">
+        <v>0.9194</v>
+      </c>
+      <c r="N9" s="9">
+        <v>0.93189999999999995</v>
+      </c>
+      <c r="O9" s="9">
+        <v>0.86629999999999996</v>
+      </c>
+      <c r="P9" s="9">
+        <v>0.96779999999999999</v>
       </c>
       <c r="Q9" s="8">
-        <v>0.71</v>
-      </c>
-      <c r="R9" s="10">
+        <v>0.68700000000000006</v>
+      </c>
+      <c r="R9" s="13">
         <f>Q9*0.95</f>
-        <v>0.67449999999999999</v>
-      </c>
-      <c r="S9" s="10">
+        <v>0.65265000000000006</v>
+      </c>
+      <c r="S9" s="13">
         <f>R9*1.05</f>
-        <v>0.70822499999999999</v>
+        <v>0.68528250000000013</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>72</v>
-      </c>
-      <c r="F10" s="8">
-        <v>0.93</v>
-      </c>
-      <c r="G10" s="8">
-        <v>7.0000000000000007E-2</v>
+        <v>68</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0.56188888888888899</v>
+      </c>
+      <c r="G10" s="9">
+        <v>8.6999999999999994E-2</v>
       </c>
       <c r="H10" s="10">
         <f>1-SUM(F10:G10,I10)</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="8">
-        <v>0</v>
+        <v>0.23711111111111105</v>
+      </c>
+      <c r="I10" s="11">
+        <v>0.114</v>
       </c>
       <c r="J10" s="12">
         <f>SUM(F10:I10)</f>
         <v>1</v>
       </c>
-      <c r="K10" s="8">
-        <v>0.622</v>
-      </c>
-      <c r="L10" s="13">
-        <f>K10*0.94</f>
-        <v>0.58467999999999998</v>
-      </c>
-      <c r="M10" s="13">
-        <f>L10*1.06</f>
-        <v>0.6197608</v>
-      </c>
-      <c r="N10" s="8">
-        <v>0.95176181599999998</v>
-      </c>
-      <c r="O10" s="8">
-        <f>N10*0.95</f>
-        <v>0.90417372519999994</v>
-      </c>
-      <c r="P10" s="8">
-        <f>N10*1.05</f>
-        <v>0.99934990680000002</v>
+      <c r="K10" s="9">
+        <v>0.81159999999999999</v>
+      </c>
+      <c r="L10" s="9">
+        <v>0.70010000000000006</v>
+      </c>
+      <c r="M10" s="9">
+        <v>0.93319999999999992</v>
+      </c>
+      <c r="N10" s="9">
+        <v>0.95489999999999997</v>
+      </c>
+      <c r="O10" s="9">
+        <v>0.90229999999999999</v>
+      </c>
+      <c r="P10" s="9">
+        <v>0.98790000000000011</v>
       </c>
       <c r="Q10" s="8">
-        <v>0.60399999999999998</v>
-      </c>
-      <c r="R10" s="10">
+        <v>0.68700000000000006</v>
+      </c>
+      <c r="R10" s="13">
         <f>Q10*0.95</f>
-        <v>0.57379999999999998</v>
-      </c>
-      <c r="S10" s="10">
+        <v>0.65265000000000006</v>
+      </c>
+      <c r="S10" s="13">
         <f>R10*1.05</f>
-        <v>0.60248999999999997</v>
+        <v>0.68528250000000013</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
-        <v>72</v>
-      </c>
-      <c r="F11" s="8">
-        <f>AVERAGE(420.2,405.3,420.2,403.8,390.7,468.4)/1000</f>
-        <v>0.41809999999999997</v>
-      </c>
-      <c r="G11" s="8">
-        <f>AVERAGE(175.4,153.9,171.8,132.3,106.7,100.1)/1000</f>
-        <v>0.14003333333333337</v>
+        <v>68</v>
+      </c>
+      <c r="F11" s="9">
+        <v>0.62166666666666659</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0.122</v>
       </c>
       <c r="H11" s="10">
         <f>1-SUM(F11:G11,I11)</f>
-        <v>0.41068333333333329</v>
-      </c>
-      <c r="I11" s="8">
-        <f>AVERAGE(28.6,37.6,28,37.3,25.9,29.7)/1000</f>
-        <v>3.1183333333333334E-2</v>
+        <v>0.14233333333333342</v>
+      </c>
+      <c r="I11" s="11">
+        <v>0.114</v>
       </c>
       <c r="J11" s="12">
         <f>SUM(F11:I11)</f>
         <v>1</v>
       </c>
-      <c r="K11" s="8">
-        <f>AVERAGE(89.5,89.3,87.9,88.2,89.3,90.1)/100</f>
-        <v>0.89050000000000007</v>
-      </c>
-      <c r="L11" s="8">
-        <f>MIN(89.5,89.3,87.9,88.2,89.3,90.1)/100</f>
-        <v>0.879</v>
-      </c>
-      <c r="M11" s="8">
-        <f>MAX(89.5,89.3,87.9,88.2,89.3,90.1)/100</f>
-        <v>0.90099999999999991</v>
-      </c>
-      <c r="N11" s="8">
-        <v>0.95176181599999998</v>
-      </c>
-      <c r="O11" s="8">
-        <f>N11*0.95</f>
-        <v>0.90417372519999994</v>
-      </c>
-      <c r="P11" s="8">
-        <f>N11*1.05</f>
-        <v>0.99934990680000002</v>
+      <c r="K11" s="9">
+        <v>0.78639999999999999</v>
+      </c>
+      <c r="L11" s="9">
+        <v>0.71209999999999996</v>
+      </c>
+      <c r="M11" s="9">
+        <v>0.84200000000000008</v>
+      </c>
+      <c r="N11" s="9">
+        <v>0.9325</v>
+      </c>
+      <c r="O11" s="9">
+        <v>0.91139999999999999</v>
+      </c>
+      <c r="P11" s="9">
+        <v>0.94950000000000001</v>
       </c>
       <c r="Q11" s="8">
-        <f>AVERAGE(79.7,80.2,80,80,81.2,77.4)/100</f>
-        <v>0.79749999999999999</v>
-      </c>
-      <c r="R11" s="8">
-        <f>MIN(79.7,80.2,80,80,81.2,77.4)/100</f>
-        <v>0.77400000000000002</v>
-      </c>
-      <c r="S11" s="8">
-        <f>MAX(79.7,80.2,80,80,81.2,77.4)/100</f>
-        <v>0.81200000000000006</v>
+        <v>0.68900000000000006</v>
+      </c>
+      <c r="R11" s="13">
+        <f>Q11*0.95</f>
+        <v>0.65455000000000008</v>
+      </c>
+      <c r="S11" s="13">
+        <f>R11*1.05</f>
+        <v>0.6872775000000001</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E12" t="s">
-        <v>72</v>
-      </c>
-      <c r="F12" s="8">
-        <v>0</v>
-      </c>
-      <c r="G12" s="8">
-        <v>0</v>
-      </c>
-      <c r="H12" s="8">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0.72292857142857125</v>
+      </c>
+      <c r="G12" s="9">
+        <f>11.68969/100</f>
+        <v>0.11689690000000001</v>
+      </c>
+      <c r="H12" s="10">
+        <f>1-SUM(F12:G12,I12)</f>
+        <v>5.4174528571428793E-2</v>
       </c>
       <c r="I12" s="8">
-        <v>1</v>
+        <v>0.106</v>
       </c>
       <c r="J12" s="12">
         <f>SUM(F12:I12)</f>
         <v>1</v>
       </c>
-      <c r="K12" s="8">
-        <v>0</v>
-      </c>
-      <c r="L12" s="8">
-        <v>0</v>
-      </c>
-      <c r="M12" s="8">
-        <v>0</v>
-      </c>
-      <c r="N12" s="8">
-        <v>0</v>
-      </c>
-      <c r="O12" s="8">
-        <f>N12*0.95</f>
-        <v>0</v>
-      </c>
-      <c r="P12" s="8">
-        <f>N12*1.05</f>
-        <v>0</v>
+      <c r="K12" s="9">
+        <v>0.86609999999999998</v>
+      </c>
+      <c r="L12" s="9">
+        <v>0.79749999999999999</v>
+      </c>
+      <c r="M12" s="9">
+        <v>0.93370000000000009</v>
+      </c>
+      <c r="N12" s="9">
+        <v>0.94900000000000007</v>
+      </c>
+      <c r="O12" s="9">
+        <v>0.90069999999999995</v>
+      </c>
+      <c r="P12" s="9">
+        <v>0.98250000000000004</v>
       </c>
       <c r="Q12" s="8">
-        <v>0</v>
+        <v>0.68899999999999995</v>
       </c>
       <c r="R12" s="13">
         <f>Q12*0.95</f>
-        <v>0</v>
+        <v>0.65454999999999997</v>
       </c>
       <c r="S12" s="13">
         <f>R12*1.05</f>
-        <v>0</v>
+        <v>0.68727749999999999</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" s="8">
-        <v>0.84</v>
-      </c>
-      <c r="G13" s="8">
-        <v>0.05</v>
-      </c>
-      <c r="H13" s="8">
-        <v>7.0000000000000007E-2</v>
+        <v>68</v>
+      </c>
+      <c r="F13" s="9">
+        <f>81.85/100</f>
+        <v>0.81849999999999989</v>
+      </c>
+      <c r="G13" s="9">
+        <f>0.1448625</f>
+        <v>0.14486250000000001</v>
+      </c>
+      <c r="H13" s="10">
+        <f>1-SUM(F13:G13,I13)</f>
+        <v>6.6375000000000739E-3</v>
       </c>
       <c r="I13" s="8">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="J13" s="12">
         <f>SUM(F13:I13)</f>
         <v>1</v>
       </c>
-      <c r="K13" s="8">
-        <v>0.88</v>
-      </c>
-      <c r="L13" s="13">
-        <f>K13*0.94</f>
-        <v>0.82719999999999994</v>
-      </c>
-      <c r="M13" s="13">
-        <f>L13*1.06</f>
-        <v>0.87683199999999994</v>
-      </c>
-      <c r="N13" s="8">
-        <v>0.95176181599999998</v>
-      </c>
-      <c r="O13" s="8">
-        <f>N13*0.95</f>
-        <v>0.90417372519999994</v>
-      </c>
-      <c r="P13" s="8">
-        <f>N13*1.05</f>
-        <v>0.99934990680000002</v>
+      <c r="K13" s="9">
+        <v>0.88379999999999992</v>
+      </c>
+      <c r="L13" s="9">
+        <v>0.87650000000000006</v>
+      </c>
+      <c r="M13" s="9">
+        <v>0.88790000000000002</v>
+      </c>
+      <c r="N13" s="9">
+        <v>0.96579999999999999</v>
+      </c>
+      <c r="O13" s="9">
+        <v>0.94930000000000003</v>
+      </c>
+      <c r="P13" s="9">
+        <v>0.98499999999999999</v>
       </c>
       <c r="Q13" s="8">
-        <v>0.77</v>
+        <v>0.88000000000000012</v>
       </c>
       <c r="R13" s="13">
         <f>Q13*0.95</f>
-        <v>0.73149999999999993</v>
+        <v>0.83600000000000008</v>
       </c>
       <c r="S13" s="13">
         <f>R13*1.05</f>
-        <v>0.76807499999999995</v>
+        <v>0.87780000000000014</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
-        <v>72</v>
-      </c>
-      <c r="F14" s="8">
-        <v>0</v>
-      </c>
-      <c r="G14" s="8">
-        <v>1</v>
-      </c>
-      <c r="H14" s="8">
-        <v>0</v>
-      </c>
-      <c r="I14" s="8">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="H14" s="10">
+        <f>1-SUM(F14:G14,I14)</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="11">
+        <v>0.14000000000000001</v>
       </c>
       <c r="J14" s="12">
         <f>SUM(F14:I14)</f>
         <v>1</v>
       </c>
-      <c r="K14" s="8">
-        <v>0</v>
-      </c>
-      <c r="L14" s="8">
-        <f>K14*0.95</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="8">
-        <f>L14*1.05</f>
-        <v>0</v>
+      <c r="K14" s="9">
+        <v>0.94140000000000001</v>
+      </c>
+      <c r="L14" s="9">
+        <v>0.92920000000000003</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0.95040000000000002</v>
       </c>
       <c r="N14" s="9">
-        <v>0.96578520322974404</v>
+        <v>0.97010000000000007</v>
       </c>
       <c r="O14" s="9">
-        <v>0.94929975751542295</v>
+        <v>0.96840000000000004</v>
       </c>
       <c r="P14" s="9">
-        <v>0.98498861542340899</v>
+        <v>0.97239999999999993</v>
       </c>
       <c r="Q14" s="8">
-        <v>0</v>
+        <v>0.68000000000000016</v>
       </c>
       <c r="R14" s="13">
         <f>Q14*0.95</f>
-        <v>0</v>
+        <v>0.64600000000000013</v>
       </c>
       <c r="S14" s="13">
         <f>R14*1.05</f>
-        <v>0</v>
+        <v>0.67830000000000013</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s">
-        <v>72</v>
-      </c>
-      <c r="F15" s="8">
-        <v>0.13</v>
-      </c>
-      <c r="G15" s="8">
+        <v>68</v>
+      </c>
+      <c r="F15" s="9">
+        <v>0.65300000000000002</v>
+      </c>
+      <c r="G15" s="9">
         <v>0.02</v>
       </c>
       <c r="H15" s="10">
         <f>1-SUM(F15:G15,I15)</f>
-        <v>0.83000000000000007</v>
+        <v>0.2569999999999999</v>
       </c>
       <c r="I15" s="8">
-        <v>0.02</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="J15" s="12">
         <f>SUM(F15:I15)</f>
         <v>1</v>
       </c>
-      <c r="K15" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="L15" s="13">
-        <f>K15*0.94</f>
-        <v>0.84599999999999997</v>
-      </c>
-      <c r="M15" s="13">
-        <f>L15*1.06</f>
-        <v>0.89676</v>
-      </c>
-      <c r="N15" s="8">
-        <v>0.95176181599999998</v>
-      </c>
-      <c r="O15" s="8">
-        <f>N15*0.95</f>
-        <v>0.90417372519999994</v>
-      </c>
-      <c r="P15" s="8">
-        <f>N15*1.05</f>
-        <v>0.99934990680000002</v>
+      <c r="K15" s="9">
+        <v>0.89379999999999993</v>
+      </c>
+      <c r="L15" s="9">
+        <v>0.8881</v>
+      </c>
+      <c r="M15" s="9">
+        <v>0.89969999999999994</v>
+      </c>
+      <c r="N15" s="9">
+        <v>0.95799999999999996</v>
+      </c>
+      <c r="O15" s="9">
+        <v>0.9323999999999999</v>
+      </c>
+      <c r="P15" s="9">
+        <v>0.97730000000000006</v>
       </c>
       <c r="Q15" s="8">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="R15" s="13">
         <f>Q15*0.95</f>
-        <v>0.76</v>
+        <v>0.77899999999999991</v>
       </c>
       <c r="S15" s="13">
         <f>R15*1.05</f>
-        <v>0.79800000000000004</v>
+        <v>0.81794999999999995</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" s="8">
-        <f>766/1000</f>
-        <v>0.76600000000000001</v>
-      </c>
-      <c r="G16" s="8">
-        <f>74/1000</f>
-        <v>7.3999999999999996E-2</v>
+        <v>68</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0.66174999999999995</v>
+      </c>
+      <c r="G16" s="9">
+        <f>1.126924/100</f>
+        <v>1.126924E-2</v>
       </c>
       <c r="H16" s="10">
         <f>1-SUM(F16:G16,I16)</f>
-        <v>0.15300000000000002</v>
+        <v>0.25398076000000014</v>
       </c>
       <c r="I16" s="8">
-        <f>7/1000</f>
-        <v>7.0000000000000001E-3</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="J16" s="12">
         <f>SUM(F16:I16)</f>
         <v>1</v>
       </c>
-      <c r="K16" s="8">
-        <v>0.89</v>
-      </c>
-      <c r="L16" s="13">
-        <f>K16*0.94</f>
-        <v>0.83660000000000001</v>
-      </c>
-      <c r="M16" s="13">
-        <f>L16*1.06</f>
-        <v>0.88679600000000003</v>
+      <c r="K16" s="9">
+        <v>0.87599999999999989</v>
+      </c>
+      <c r="L16" s="9">
+        <v>0.8206</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0.92709999999999992</v>
       </c>
       <c r="N16" s="8">
         <v>0.95176181599999998</v>
@@ -3328,772 +3306,777 @@
         <v>0.99934990680000002</v>
       </c>
       <c r="Q16" s="8">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="R16" s="13">
         <f>Q16*0.95</f>
-        <v>0.71249999999999991</v>
+        <v>0.83124999999999993</v>
       </c>
       <c r="S16" s="13">
         <f>R16*1.05</f>
-        <v>0.74812499999999993</v>
+        <v>0.87281249999999999</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8">
         <v>1</v>
       </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" t="s">
-        <v>71</v>
-      </c>
-      <c r="E17" t="s">
-        <v>71</v>
-      </c>
-      <c r="F17" s="9">
-        <v>0.53500000000000003</v>
-      </c>
-      <c r="G17" s="9">
-        <v>0.224</v>
-      </c>
-      <c r="H17" s="10">
-        <f>1-SUM(F17:G17,I17)</f>
-        <v>0.11099999999999999</v>
+      <c r="H17" s="8">
+        <v>0</v>
       </c>
       <c r="I17" s="8">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="J17" s="12">
         <f>SUM(F17:I17)</f>
         <v>1</v>
       </c>
-      <c r="K17" s="9">
-        <v>0.86264614774680892</v>
-      </c>
-      <c r="L17" s="9">
-        <v>0.71937060515209228</v>
-      </c>
-      <c r="M17" s="9">
-        <v>0.9363167126299663</v>
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8">
+        <f>K17*0.95</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="8">
+        <f>L17*1.05</f>
+        <v>0</v>
       </c>
       <c r="N17" s="8">
-        <v>0.93</v>
+        <v>0.95176181599999998</v>
       </c>
       <c r="O17" s="8">
         <f>N17*0.95</f>
-        <v>0.88349999999999995</v>
+        <v>0.90417372519999994</v>
       </c>
       <c r="P17" s="8">
         <f>N17*1.05</f>
-        <v>0.97650000000000015</v>
+        <v>0.99934990680000002</v>
       </c>
       <c r="Q17" s="8">
-        <v>0.41000000000000003</v>
+        <v>0</v>
       </c>
       <c r="R17" s="10">
         <f>Q17*0.95</f>
-        <v>0.38950000000000001</v>
+        <v>0</v>
       </c>
       <c r="S17" s="10">
         <f>R17*1.05</f>
-        <v>0.40897500000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F18" s="9">
-        <v>0.32700000000000001</v>
-      </c>
-      <c r="G18" s="9">
-        <v>0.13</v>
-      </c>
-      <c r="H18" s="10">
-        <f>1-SUM(F18:G18,I18)</f>
-        <v>0.46672719298245613</v>
-      </c>
-      <c r="I18" s="11">
-        <v>7.6272807017543895E-2</v>
+        <v>69</v>
+      </c>
+      <c r="F18" s="8">
+        <v>0</v>
+      </c>
+      <c r="G18" s="8">
+        <v>0</v>
+      </c>
+      <c r="H18" s="8">
+        <v>0</v>
+      </c>
+      <c r="I18" s="8">
+        <v>1</v>
       </c>
       <c r="J18" s="12">
         <f>SUM(F18:I18)</f>
         <v>1</v>
       </c>
-      <c r="K18" s="9">
-        <v>0.91108708069547573</v>
-      </c>
-      <c r="L18" s="9">
-        <v>0.88845319139472811</v>
-      </c>
-      <c r="M18" s="9">
-        <v>0.93104235892070819</v>
+      <c r="K18" s="8">
+        <v>0</v>
+      </c>
+      <c r="L18" s="8">
+        <v>0</v>
+      </c>
+      <c r="M18" s="8">
+        <v>0</v>
       </c>
       <c r="N18" s="8">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="O18" s="8">
         <f>N18*0.95</f>
-        <v>0.88349999999999995</v>
+        <v>0</v>
       </c>
       <c r="P18" s="8">
         <f>N18*1.05</f>
-        <v>0.97650000000000015</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="8">
-        <v>0.68600000000000005</v>
+        <v>0</v>
       </c>
       <c r="R18" s="10">
         <f>Q18*0.95</f>
-        <v>0.65170000000000006</v>
+        <v>0</v>
       </c>
       <c r="S18" s="10">
         <f>R18*1.05</f>
-        <v>0.68428500000000014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E19" t="s">
-        <v>71</v>
-      </c>
-      <c r="F19" s="9">
-        <v>0.86849038461538397</v>
-      </c>
-      <c r="G19" s="9">
-        <f>6.7799419/100</f>
-        <v>6.7799419E-2</v>
-      </c>
-      <c r="H19" s="10">
-        <f>1-SUM(F19:G19,I19)</f>
-        <v>1.3710196384616014E-2</v>
+        <v>69</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8">
+        <v>1</v>
+      </c>
+      <c r="H19" s="8">
+        <v>0</v>
       </c>
       <c r="I19" s="8">
-        <f>5/100</f>
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J19" s="12">
         <f>SUM(F19:I19)</f>
         <v>1</v>
       </c>
-      <c r="K19" s="9">
-        <v>0.86596964644311503</v>
-      </c>
-      <c r="L19" s="9">
-        <v>0.75831666847301604</v>
-      </c>
-      <c r="M19" s="9">
-        <v>0.94739830238765299</v>
-      </c>
-      <c r="N19" s="9">
-        <v>0.93708838073277401</v>
-      </c>
-      <c r="O19" s="9">
-        <v>0.87281262552261096</v>
-      </c>
-      <c r="P19" s="9">
-        <v>0.97951322885623004</v>
+      <c r="K19" s="8">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8">
+        <f>K19*0.95</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="8">
+        <f>L19*1.05</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="8">
+        <v>0.95176181599999998</v>
+      </c>
+      <c r="O19" s="8">
+        <f>N19*0.95</f>
+        <v>0.90417372519999994</v>
+      </c>
+      <c r="P19" s="8">
+        <f>N19*1.05</f>
+        <v>0.99934990680000002</v>
       </c>
       <c r="Q19" s="8">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="R19" s="10">
         <f>Q19*0.95</f>
-        <v>0.74099999999999999</v>
+        <v>0</v>
       </c>
       <c r="S19" s="10">
         <f>R19*1.05</f>
-        <v>0.77805000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E20" t="s">
-        <v>71</v>
-      </c>
-      <c r="F20" s="9">
-        <v>0.55099999999999993</v>
-      </c>
-      <c r="G20" s="9">
-        <f>26.92252/100</f>
-        <v>0.2692252</v>
-      </c>
-      <c r="H20" s="10">
-        <f>1-SUM(F20:G20,I20)</f>
-        <v>4.08748000000001E-2</v>
+        <v>69</v>
+      </c>
+      <c r="F20" s="8">
+        <v>0</v>
+      </c>
+      <c r="G20" s="8">
+        <v>1</v>
+      </c>
+      <c r="H20" s="8">
+        <v>0</v>
       </c>
       <c r="I20" s="8">
-        <f>13.89/100</f>
-        <v>0.1389</v>
+        <v>0</v>
       </c>
       <c r="J20" s="12">
         <f>SUM(F20:I20)</f>
         <v>1</v>
       </c>
-      <c r="K20" s="9">
-        <v>0.877686516894431</v>
-      </c>
-      <c r="L20" s="9">
-        <v>0.86929340553071399</v>
-      </c>
-      <c r="M20" s="9">
-        <v>0.88552039033038199</v>
+      <c r="K20" s="8">
+        <v>0</v>
+      </c>
+      <c r="L20" s="8">
+        <f>K20*0.95</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="8">
+        <f>L20*1.05</f>
+        <v>0</v>
       </c>
       <c r="N20" s="9">
-        <v>0.95114829052565797</v>
+        <v>0.95669999999999999</v>
       </c>
       <c r="O20" s="9">
-        <v>0.93888547813119905</v>
+        <v>0.8993000000000001</v>
       </c>
       <c r="P20" s="9">
-        <v>0.95743188023568604</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="Q20" s="8">
-        <v>0.59399999999999997</v>
-      </c>
-      <c r="R20" s="8">
-        <f>Q20-3*(2.16/100)</f>
-        <v>0.5292</v>
-      </c>
-      <c r="S20" s="8">
-        <f>Q20+3*(2.16/100)</f>
-        <v>0.65879999999999994</v>
+        <v>0</v>
+      </c>
+      <c r="R20" s="10">
+        <f>Q20*0.95</f>
+        <v>0</v>
+      </c>
+      <c r="S20" s="10">
+        <f>R20*1.05</f>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E21" t="s">
-        <v>71</v>
-      </c>
-      <c r="F21" s="9">
-        <v>0.53783333333333327</v>
-      </c>
-      <c r="G21" s="9">
-        <f>13.249433/100</f>
-        <v>0.13249432999999999</v>
-      </c>
-      <c r="H21" s="10">
-        <f>1-SUM(F21:G21,I21)</f>
-        <v>2.4672336666666794E-2</v>
+        <v>69</v>
+      </c>
+      <c r="F21" s="8">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8">
+        <v>1</v>
+      </c>
+      <c r="H21" s="8">
+        <v>0</v>
       </c>
       <c r="I21" s="8">
-        <v>0.30499999999999999</v>
+        <v>0</v>
       </c>
       <c r="J21" s="12">
         <f>SUM(F21:I21)</f>
         <v>1</v>
       </c>
-      <c r="K21" s="9">
-        <v>0.83030542718534806</v>
-      </c>
-      <c r="L21" s="9">
-        <v>0.72499626396843597</v>
-      </c>
-      <c r="M21" s="9">
-        <v>0.91940803995423603</v>
+      <c r="K21" s="8">
+        <v>0</v>
+      </c>
+      <c r="L21" s="8">
+        <f>K21*0.95</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="8">
+        <f>L21*1.05</f>
+        <v>0</v>
       </c>
       <c r="N21" s="9">
-        <v>0.93189462648181998</v>
+        <v>0.95669999999999999</v>
       </c>
       <c r="O21" s="9">
-        <v>0.86627011737210602</v>
+        <v>0.8993000000000001</v>
       </c>
       <c r="P21" s="9">
-        <v>0.96776157310788602</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="Q21" s="8">
-        <v>0.68700000000000006</v>
-      </c>
-      <c r="R21" s="13">
+        <v>0</v>
+      </c>
+      <c r="R21" s="10">
         <f>Q21*0.95</f>
-        <v>0.65265000000000006</v>
-      </c>
-      <c r="S21" s="13">
+        <v>0</v>
+      </c>
+      <c r="S21" s="10">
         <f>R21*1.05</f>
-        <v>0.68528250000000013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" t="s">
         <v>69</v>
       </c>
-      <c r="B22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" t="s">
-        <v>72</v>
-      </c>
-      <c r="D22" t="s">
-        <v>71</v>
-      </c>
-      <c r="E22" t="s">
-        <v>71</v>
-      </c>
-      <c r="F22" s="9">
-        <v>0.56188888888888899</v>
-      </c>
-      <c r="G22" s="9">
-        <v>8.6999999999999994E-2</v>
-      </c>
-      <c r="H22" s="10">
-        <f>1-SUM(F22:G22,I22)</f>
-        <v>0.23711111111111105</v>
-      </c>
-      <c r="I22" s="11">
-        <v>0.114</v>
+      <c r="F22" s="8">
+        <v>0.42</v>
+      </c>
+      <c r="G22" s="8">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="H22" s="8">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="I22" s="8">
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="J22" s="12">
         <f>SUM(F22:I22)</f>
         <v>1</v>
       </c>
-      <c r="K22" s="9">
-        <v>0.81159790994043479</v>
-      </c>
-      <c r="L22" s="9">
-        <v>0.70014233740626763</v>
-      </c>
-      <c r="M22" s="9">
-        <v>0.93324792899801945</v>
+      <c r="K22" s="8">
+        <v>0.63000000000000012</v>
+      </c>
+      <c r="L22" s="13">
+        <f>K22*0.95</f>
+        <v>0.59850000000000003</v>
+      </c>
+      <c r="M22" s="13">
+        <f>L22*1.05</f>
+        <v>0.62842500000000001</v>
       </c>
       <c r="N22" s="8">
-        <v>0.93</v>
+        <v>0.95176181599999998</v>
       </c>
       <c r="O22" s="8">
         <f>N22*0.95</f>
-        <v>0.88349999999999995</v>
+        <v>0.90417372519999994</v>
       </c>
       <c r="P22" s="8">
         <f>N22*1.05</f>
-        <v>0.97650000000000015</v>
+        <v>0.99934990680000002</v>
       </c>
       <c r="Q22" s="8">
-        <v>0.68700000000000006</v>
-      </c>
-      <c r="R22" s="13">
+        <v>0.71</v>
+      </c>
+      <c r="R22" s="10">
         <f>Q22*0.95</f>
-        <v>0.65265000000000006</v>
-      </c>
-      <c r="S22" s="13">
+        <v>0.67449999999999999</v>
+      </c>
+      <c r="S22" s="10">
         <f>R22*1.05</f>
-        <v>0.68528250000000013</v>
+        <v>0.70822499999999999</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E23" t="s">
-        <v>71</v>
-      </c>
-      <c r="F23" s="9">
-        <v>0.62166666666666659</v>
-      </c>
-      <c r="G23" s="9">
-        <v>0.122</v>
+        <v>69</v>
+      </c>
+      <c r="F23" s="8">
+        <v>0.93</v>
+      </c>
+      <c r="G23" s="8">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="H23" s="10">
         <f>1-SUM(F23:G23,I23)</f>
-        <v>0.14233333333333342</v>
-      </c>
-      <c r="I23" s="11">
-        <v>0.114</v>
+        <v>0</v>
+      </c>
+      <c r="I23" s="8">
+        <v>0</v>
       </c>
       <c r="J23" s="12">
         <f>SUM(F23:I23)</f>
         <v>1</v>
       </c>
-      <c r="K23" s="9">
-        <v>0.78638081783306735</v>
-      </c>
-      <c r="L23" s="9">
-        <v>0.7121352290987818</v>
-      </c>
-      <c r="M23" s="9">
-        <v>0.84199992299760551</v>
+      <c r="K23" s="8">
+        <v>0.622</v>
+      </c>
+      <c r="L23" s="13">
+        <f>K23*0.94</f>
+        <v>0.58467999999999998</v>
+      </c>
+      <c r="M23" s="13">
+        <f>L23*1.06</f>
+        <v>0.6197608</v>
       </c>
       <c r="N23" s="8">
-        <v>0.93</v>
+        <v>0.95176181599999998</v>
       </c>
       <c r="O23" s="8">
         <f>N23*0.95</f>
-        <v>0.88349999999999995</v>
+        <v>0.90417372519999994</v>
       </c>
       <c r="P23" s="8">
         <f>N23*1.05</f>
-        <v>0.97650000000000015</v>
+        <v>0.99934990680000002</v>
       </c>
       <c r="Q23" s="8">
-        <v>0.68900000000000006</v>
-      </c>
-      <c r="R23" s="13">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="R23" s="10">
         <f>Q23*0.95</f>
-        <v>0.65455000000000008</v>
-      </c>
-      <c r="S23" s="13">
+        <v>0.57379999999999998</v>
+      </c>
+      <c r="S23" s="10">
         <f>R23*1.05</f>
-        <v>0.6872775000000001</v>
+        <v>0.60248999999999997</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D24" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E24" t="s">
-        <v>71</v>
-      </c>
-      <c r="F24" s="9">
-        <v>0.72292857142857125</v>
-      </c>
-      <c r="G24" s="9">
-        <f>11.68969/100</f>
-        <v>0.11689690000000001</v>
+        <v>69</v>
+      </c>
+      <c r="F24" s="8">
+        <f>AVERAGE(420.2,405.3,420.2,403.8,390.7,468.4)/1000</f>
+        <v>0.41809999999999997</v>
+      </c>
+      <c r="G24" s="8">
+        <f>AVERAGE(175.4,153.9,171.8,132.3,106.7,100.1)/1000</f>
+        <v>0.14003333333333337</v>
       </c>
       <c r="H24" s="10">
         <f>1-SUM(F24:G24,I24)</f>
-        <v>5.4174528571428793E-2</v>
+        <v>0.41068333333333329</v>
       </c>
       <c r="I24" s="8">
-        <v>0.106</v>
+        <f>AVERAGE(28.6,37.6,28,37.3,25.9,29.7)/1000</f>
+        <v>3.1183333333333334E-2</v>
       </c>
       <c r="J24" s="12">
         <f>SUM(F24:I24)</f>
         <v>1</v>
       </c>
-      <c r="K24" s="9">
-        <v>0.86610883281803497</v>
-      </c>
-      <c r="L24" s="9">
-        <v>0.79747397943132603</v>
-      </c>
-      <c r="M24" s="9">
-        <v>0.93373585381326696</v>
-      </c>
-      <c r="N24" s="9">
-        <v>0.94897384021576103</v>
-      </c>
-      <c r="O24" s="9">
-        <v>0.90071911597065302</v>
-      </c>
-      <c r="P24" s="9">
-        <v>0.98253169598285695</v>
+      <c r="K24" s="8">
+        <f>AVERAGE(89.5,89.3,87.9,88.2,89.3,90.1)/100</f>
+        <v>0.89050000000000007</v>
+      </c>
+      <c r="L24" s="8">
+        <f>MIN(89.5,89.3,87.9,88.2,89.3,90.1)/100</f>
+        <v>0.879</v>
+      </c>
+      <c r="M24" s="8">
+        <f>MAX(89.5,89.3,87.9,88.2,89.3,90.1)/100</f>
+        <v>0.90099999999999991</v>
+      </c>
+      <c r="N24" s="8">
+        <v>0.95176181599999998</v>
+      </c>
+      <c r="O24" s="8">
+        <f>N24*0.95</f>
+        <v>0.90417372519999994</v>
+      </c>
+      <c r="P24" s="8">
+        <f>N24*1.05</f>
+        <v>0.99934990680000002</v>
       </c>
       <c r="Q24" s="8">
-        <v>0.68899999999999995</v>
-      </c>
-      <c r="R24" s="13">
-        <f>Q24*0.95</f>
-        <v>0.65454999999999997</v>
-      </c>
-      <c r="S24" s="13">
-        <f>R24*1.05</f>
-        <v>0.68727749999999999</v>
+        <f>AVERAGE(79.7,80.2,80,80,81.2,77.4)/100</f>
+        <v>0.79749999999999999</v>
+      </c>
+      <c r="R24" s="8">
+        <f>MIN(79.7,80.2,80,80,81.2,77.4)/100</f>
+        <v>0.77400000000000002</v>
+      </c>
+      <c r="S24" s="8">
+        <f>MAX(79.7,80.2,80,80,81.2,77.4)/100</f>
+        <v>0.81200000000000006</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" t="s">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D25" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E25" t="s">
-        <v>71</v>
-      </c>
-      <c r="F25" s="9">
-        <f>81.85/100</f>
-        <v>0.81849999999999989</v>
-      </c>
-      <c r="G25" s="9">
-        <f>0.1448625</f>
-        <v>0.14486250000000001</v>
-      </c>
-      <c r="H25" s="10">
-        <f>1-SUM(F25:G25,I25)</f>
-        <v>6.6375000000000739E-3</v>
+        <v>69</v>
+      </c>
+      <c r="F25" s="8">
+        <v>0</v>
+      </c>
+      <c r="G25" s="8">
+        <v>0</v>
+      </c>
+      <c r="H25" s="8">
+        <v>0</v>
       </c>
       <c r="I25" s="8">
-        <v>0.03</v>
+        <v>1</v>
       </c>
       <c r="J25" s="12">
         <f>SUM(F25:I25)</f>
         <v>1</v>
       </c>
-      <c r="K25" s="9">
-        <v>0.88381879361953897</v>
-      </c>
-      <c r="L25" s="9">
-        <v>0.87650883500487797</v>
-      </c>
-      <c r="M25" s="9">
-        <v>0.88785013351798403</v>
-      </c>
-      <c r="N25" s="9">
-        <v>0.96578520322974404</v>
-      </c>
-      <c r="O25" s="9">
-        <v>0.94929975751542295</v>
-      </c>
-      <c r="P25" s="9">
-        <v>0.98498861542340899</v>
+      <c r="K25" s="8">
+        <v>0</v>
+      </c>
+      <c r="L25" s="8">
+        <v>0</v>
+      </c>
+      <c r="M25" s="8">
+        <v>0</v>
+      </c>
+      <c r="N25" s="8">
+        <v>0</v>
+      </c>
+      <c r="O25" s="8">
+        <f>N25*0.95</f>
+        <v>0</v>
+      </c>
+      <c r="P25" s="8">
+        <f>N25*1.05</f>
+        <v>0</v>
       </c>
       <c r="Q25" s="8">
-        <v>0.88000000000000012</v>
+        <v>0</v>
       </c>
       <c r="R25" s="13">
         <f>Q25*0.95</f>
-        <v>0.83600000000000008</v>
+        <v>0</v>
       </c>
       <c r="S25" s="13">
         <f>R25*1.05</f>
-        <v>0.87780000000000014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E26" t="s">
-        <v>71</v>
-      </c>
-      <c r="F26" s="9">
-        <v>0.75900000000000001</v>
-      </c>
-      <c r="G26" s="9">
-        <v>0.10100000000000001</v>
-      </c>
-      <c r="H26" s="10">
-        <f>1-SUM(F26:G26,I26)</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="11">
-        <v>0.14000000000000001</v>
+        <v>69</v>
+      </c>
+      <c r="F26" s="8">
+        <v>0.84</v>
+      </c>
+      <c r="G26" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="H26" s="8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I26" s="8">
+        <v>0.04</v>
       </c>
       <c r="J26" s="12">
         <f>SUM(F26:I26)</f>
         <v>1</v>
       </c>
-      <c r="K26" s="9">
-        <v>0.94144621422710895</v>
-      </c>
-      <c r="L26" s="9">
-        <v>0.92915488186404305</v>
-      </c>
-      <c r="M26" s="9">
-        <v>0.95038279881441345</v>
+      <c r="K26" s="8">
+        <v>0.88</v>
+      </c>
+      <c r="L26" s="13">
+        <f>K26*0.94</f>
+        <v>0.82719999999999994</v>
+      </c>
+      <c r="M26" s="13">
+        <f>L26*1.06</f>
+        <v>0.87683199999999994</v>
       </c>
       <c r="N26" s="8">
-        <v>0.93</v>
+        <v>0.95176181599999998</v>
       </c>
       <c r="O26" s="8">
         <f>N26*0.95</f>
-        <v>0.88349999999999995</v>
+        <v>0.90417372519999994</v>
       </c>
       <c r="P26" s="8">
         <f>N26*1.05</f>
-        <v>0.97650000000000015</v>
+        <v>0.99934990680000002</v>
       </c>
       <c r="Q26" s="8">
-        <v>0.68000000000000016</v>
+        <v>0.77</v>
       </c>
       <c r="R26" s="13">
         <f>Q26*0.95</f>
-        <v>0.64600000000000013</v>
+        <v>0.73149999999999993</v>
       </c>
       <c r="S26" s="13">
         <f>R26*1.05</f>
-        <v>0.67830000000000013</v>
+        <v>0.76807499999999995</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C27" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D27" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E27" t="s">
-        <v>71</v>
-      </c>
-      <c r="F27" s="9">
-        <v>0.65300000000000002</v>
-      </c>
-      <c r="G27" s="9">
-        <v>0.02</v>
-      </c>
-      <c r="H27" s="10">
-        <f>1-SUM(F27:G27,I27)</f>
-        <v>0.2569999999999999</v>
+        <v>69</v>
+      </c>
+      <c r="F27" s="8">
+        <v>0</v>
+      </c>
+      <c r="G27" s="8">
+        <v>1</v>
+      </c>
+      <c r="H27" s="8">
+        <v>0</v>
       </c>
       <c r="I27" s="8">
-        <v>7.0000000000000007E-2</v>
+        <v>0</v>
       </c>
       <c r="J27" s="12">
         <f>SUM(F27:I27)</f>
         <v>1</v>
       </c>
-      <c r="K27" s="9">
-        <v>0.8937733673883973</v>
-      </c>
-      <c r="L27" s="9">
-        <v>0.88807945048616632</v>
-      </c>
-      <c r="M27" s="9">
-        <v>0.89967859362798408</v>
-      </c>
-      <c r="N27" s="8">
-        <v>0.93</v>
-      </c>
-      <c r="O27" s="8">
-        <f>N27*0.95</f>
-        <v>0.88349999999999995</v>
-      </c>
-      <c r="P27" s="8">
-        <f>N27*1.05</f>
-        <v>0.97650000000000015</v>
+      <c r="K27" s="8">
+        <v>0</v>
+      </c>
+      <c r="L27" s="8">
+        <f>K27*0.95</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="8">
+        <f>L27*1.05</f>
+        <v>0</v>
+      </c>
+      <c r="N27" s="9">
+        <v>0.94900000000000007</v>
+      </c>
+      <c r="O27" s="9">
+        <v>0.90069999999999995</v>
+      </c>
+      <c r="P27" s="9">
+        <v>0.98250000000000004</v>
       </c>
       <c r="Q27" s="8">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="R27" s="13">
         <f>Q27*0.95</f>
-        <v>0.77899999999999991</v>
+        <v>0</v>
       </c>
       <c r="S27" s="13">
         <f>R27*1.05</f>
-        <v>0.81794999999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D28" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E28" t="s">
-        <v>71</v>
-      </c>
-      <c r="F28" s="9">
-        <v>0.66174999999999995</v>
-      </c>
-      <c r="G28" s="9">
-        <f>1.126924/100</f>
-        <v>1.126924E-2</v>
+        <v>69</v>
+      </c>
+      <c r="F28" s="8">
+        <v>0.13</v>
+      </c>
+      <c r="G28" s="8">
+        <v>0.02</v>
       </c>
       <c r="H28" s="10">
         <f>1-SUM(F28:G28,I28)</f>
-        <v>0.25398076000000014</v>
+        <v>0.83000000000000007</v>
       </c>
       <c r="I28" s="8">
-        <v>7.2999999999999995E-2</v>
+        <v>0.02</v>
       </c>
       <c r="J28" s="12">
         <f>SUM(F28:I28)</f>
         <v>1</v>
       </c>
-      <c r="K28" s="9">
-        <v>0.87600843567991205</v>
-      </c>
-      <c r="L28" s="9">
-        <v>0.82061188906613203</v>
-      </c>
-      <c r="M28" s="9">
-        <v>0.92710478819527697</v>
+      <c r="K28" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="L28" s="13">
+        <f>K28*0.94</f>
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="M28" s="13">
+        <f>L28*1.06</f>
+        <v>0.89676</v>
       </c>
       <c r="N28" s="8">
         <v>0.95176181599999998</v>
@@ -4107,100 +4090,109 @@
         <v>0.99934990680000002</v>
       </c>
       <c r="Q28" s="8">
-        <v>0.875</v>
+        <v>0.8</v>
       </c>
       <c r="R28" s="13">
         <f>Q28*0.95</f>
-        <v>0.83124999999999993</v>
+        <v>0.76</v>
       </c>
       <c r="S28" s="13">
         <f>R28*1.05</f>
-        <v>0.87281249999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
-    </row>
-    <row r="36" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
-    </row>
-    <row r="37" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
-    </row>
-    <row r="38" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
-    </row>
-    <row r="39" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L39" s="5"/>
-      <c r="M39" s="5"/>
-    </row>
-    <row r="40" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
-    </row>
-    <row r="41" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L41" s="5"/>
-      <c r="M41" s="5"/>
-    </row>
-    <row r="42" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L42" s="5"/>
-      <c r="M42" s="5"/>
-    </row>
-    <row r="43" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L43" s="5"/>
-      <c r="M43" s="5"/>
-    </row>
-    <row r="44" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L44" s="5"/>
-      <c r="M44" s="5"/>
-    </row>
-    <row r="45" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L45" s="5"/>
-      <c r="M45" s="5"/>
-    </row>
-    <row r="46" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L46" s="5"/>
-      <c r="M46" s="5"/>
-    </row>
-    <row r="47" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L47" s="5"/>
-      <c r="M47" s="5"/>
-    </row>
-    <row r="48" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L48" s="5"/>
-      <c r="M48" s="5"/>
-    </row>
-    <row r="49" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L49" s="5"/>
-      <c r="M49" s="5"/>
-    </row>
-    <row r="50" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L50" s="5"/>
-      <c r="M50" s="5"/>
-    </row>
-    <row r="51" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L51" s="5"/>
-      <c r="M51" s="5"/>
-    </row>
-    <row r="52" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L52" s="5"/>
-      <c r="M52" s="5"/>
-    </row>
-    <row r="53" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L53" s="5"/>
-      <c r="M53" s="5"/>
+        <v>0.79800000000000004</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" t="s">
+        <v>69</v>
+      </c>
+      <c r="F29" s="8">
+        <f>766/1000</f>
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="G29" s="8">
+        <f>74/1000</f>
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="H29" s="10">
+        <f>1-SUM(F29:G29,I29)</f>
+        <v>0.15300000000000002</v>
+      </c>
+      <c r="I29" s="8">
+        <f>7/1000</f>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="J29" s="12">
+        <f>SUM(F29:I29)</f>
+        <v>1</v>
+      </c>
+      <c r="K29" s="8">
+        <v>0.89</v>
+      </c>
+      <c r="L29" s="13">
+        <f>K29*0.94</f>
+        <v>0.83660000000000001</v>
+      </c>
+      <c r="M29" s="13">
+        <f>L29*1.06</f>
+        <v>0.88679600000000003</v>
+      </c>
+      <c r="N29" s="8">
+        <v>0.95176181599999998</v>
+      </c>
+      <c r="O29" s="8">
+        <f>N29*0.95</f>
+        <v>0.90417372519999994</v>
+      </c>
+      <c r="P29" s="8">
+        <f>N29*1.05</f>
+        <v>0.99934990680000002</v>
+      </c>
+      <c r="Q29" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="R29" s="13">
+        <f>Q29*0.95</f>
+        <v>0.71249999999999991</v>
+      </c>
+      <c r="S29" s="13">
+        <f>R29*1.05</f>
+        <v>0.74812499999999993</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="M31" s="5"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+    </row>
+    <row r="33" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+    </row>
+    <row r="34" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S53" xr:uid="{FEB86C80-6855-4296-9746-1E92B0D65FFA}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S53">
-      <sortCondition ref="E1:E53"/>
+  <autoFilter ref="A1:S29" xr:uid="{FEB86C80-6855-4296-9746-1E92B0D65FFA}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S29">
+      <sortCondition descending="1" ref="E1:E29"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="K2:S28">
+  <conditionalFormatting sqref="K2:S29">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
@@ -4230,16 +4222,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>43</v>
@@ -4254,7 +4246,7 @@
         <v>45</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>40</v>
@@ -4289,16 +4281,16 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F2" s="8">
         <v>0</v>
@@ -4355,16 +4347,16 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F3" s="8">
         <v>0.68</v>
@@ -4422,16 +4414,16 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F4">
         <v>0.3</v>
@@ -4489,16 +4481,16 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F5">
         <v>0.55800000000000005</v>
@@ -4555,16 +4547,16 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -4621,16 +4613,16 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F7">
         <v>0.23</v>
@@ -4687,16 +4679,16 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -4753,16 +4745,16 @@
         <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F9">
         <v>0.63800000000000001</v>
@@ -4820,16 +4812,16 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F10">
         <v>0.32400000000000001</v>
@@ -4886,16 +4878,16 @@
         <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F11">
         <v>0.377</v>
@@ -4952,16 +4944,16 @@
         <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F12">
         <v>2.9000000000000001E-2</v>
@@ -5018,16 +5010,16 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F13">
         <v>0.48</v>
@@ -5204,62 +5196,62 @@
         <v>0</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L1" s="2"/>
       <c r="M1" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="N1" s="2"/>
       <c r="O1" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P1" s="2"/>
       <c r="Q1" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="W1" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="X1" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="X1" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="Y1" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="2:25" x14ac:dyDescent="0.3">
       <c r="J2" t="s">
         <v>47</v>
       </c>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15">
+      <c r="K2" s="14"/>
+      <c r="L2" s="14">
         <f>K2*GETPIVOTDATA("Sum of protein",$B$3,"ingredient",$J2)*GETPIVOTDATA("Sum of mean_protein_digestibility",$B$3,"ingredient",$J2)*23.6+K2*GETPIVOTDATA("Sum of lipid",$B$3,"ingredient",$J2)*GETPIVOTDATA("Sum of mean_lipid_digestibility",$B$3,"ingredient",$J2)*36.2+K2*GETPIVOTDATA("Sum of carb",$B$3,"ingredient",$J2)*GETPIVOTDATA("Sum of mean_carb_digestibility",$B$3,"ingredient",$J2)*17.2</f>
         <v>0</v>
       </c>
-      <c r="M2" s="15">
+      <c r="M2" s="14">
         <v>4.7600000000000003E-2</v>
       </c>
-      <c r="N2" s="15">
+      <c r="N2" s="14">
         <f>M2*GETPIVOTDATA("Sum of protein",$B$3,"ingredient",$J2)*GETPIVOTDATA("Sum of mean_protein_digestibility",$B$3,"ingredient",$J2)*23.6+M2*GETPIVOTDATA("Sum of lipid",$B$3,"ingredient",$J2)*GETPIVOTDATA("Sum of mean_lipid_digestibility",$B$3,"ingredient",$J2)*36.2+M2*GETPIVOTDATA("Sum of carb",$B$3,"ingredient",$J2)*GETPIVOTDATA("Sum of mean_carb_digestibility",$B$3,"ingredient",$J2)*17.2</f>
         <v>1.6399998203859201</v>
       </c>
-      <c r="O2" s="15">
+      <c r="O2" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="P2">
@@ -5267,7 +5259,7 @@
         <v>0.86134444348000017</v>
       </c>
       <c r="Q2" s="8"/>
-      <c r="R2" s="19">
+      <c r="R2" s="18">
         <f>Q2*GETPIVOTDATA("Sum of protein",$B$3,"ingredient",$J2)*GETPIVOTDATA("Sum of mean_protein_digestibility",$B$3,"ingredient",$J2)*23.6+Q2*GETPIVOTDATA("Sum of lipid",$B$3,"ingredient",$J2)*GETPIVOTDATA("Sum of mean_lipid_digestibility",$B$3,"ingredient",$J2)*36.2+Q2*GETPIVOTDATA("Sum of carb",$B$3,"ingredient",$J2)*GETPIVOTDATA("Sum of mean_carb_digestibility",$B$3,"ingredient",$J2)*17.2</f>
         <v>0</v>
       </c>
@@ -5279,7 +5271,7 @@
         <f>M2/SUM(M$2:M$39)</f>
         <v>4.1071814505501562E-2</v>
       </c>
-      <c r="U2" s="19">
+      <c r="U2" s="18">
         <f>T2*GETPIVOTDATA("Sum of protein",$B$3,"ingredient",$J2)*GETPIVOTDATA("Sum of mean_protein_digestibility",$B$3,"ingredient",$J2)*23.6+T2*GETPIVOTDATA("Sum of lipid",$B$3,"ingredient",$J2)*GETPIVOTDATA("Sum of mean_lipid_digestibility",$B$3,"ingredient",$J2)*36.2+T2*GETPIVOTDATA("Sum of carb",$B$3,"ingredient",$J2)*GETPIVOTDATA("Sum of mean_carb_digestibility",$B$3,"ingredient",$J2)*17.2</f>
         <v>1.4150791683182014</v>
       </c>
@@ -5291,7 +5283,7 @@
         <f>O2/SUM(O$2:O$39)</f>
         <v>2.6758309066129467E-2</v>
       </c>
-      <c r="X2" s="19">
+      <c r="X2" s="18">
         <f>W2*GETPIVOTDATA("Sum of protein",$B$3,"ingredient",$J2)*GETPIVOTDATA("Sum of mean_protein_digestibility",$B$3,"ingredient",$J2)*23.6+W2*GETPIVOTDATA("Sum of lipid",$B$3,"ingredient",$J2)*GETPIVOTDATA("Sum of mean_lipid_digestibility",$B$3,"ingredient",$J2)*36.2+W2*GETPIVOTDATA("Sum of carb",$B$3,"ingredient",$J2)*GETPIVOTDATA("Sum of mean_carb_digestibility",$B$3,"ingredient",$J2)*17.2</f>
         <v>0.92192483324124497</v>
       </c>
@@ -5302,38 +5294,38 @@
     </row>
     <row r="3" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B3" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G3" t="s">
         <v>90</v>
       </c>
-      <c r="C3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>93</v>
-      </c>
-      <c r="H3" t="s">
-        <v>96</v>
       </c>
       <c r="J3" t="s">
         <v>48</v>
       </c>
-      <c r="K3" s="17">
+      <c r="K3" s="16">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="L3" s="15"/>
-      <c r="M3" s="17">
+      <c r="L3" s="14"/>
+      <c r="M3" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="N3" s="15"/>
-      <c r="O3" s="17">
+      <c r="N3" s="14"/>
+      <c r="O3" s="16">
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="P3">
@@ -5344,7 +5336,7 @@
         <f>K3/SUM(K$2:K$39)</f>
         <v>2.5997400259973997E-3</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="18">
         <f t="shared" ref="R3:R38" si="1">Q3*GETPIVOTDATA("Sum of protein",$B$3,"ingredient",$J3)*GETPIVOTDATA("Sum of mean_protein_digestibility",$B$3,"ingredient",$J3)*23.6+Q3*GETPIVOTDATA("Sum of lipid",$B$3,"ingredient",$J3)*GETPIVOTDATA("Sum of mean_lipid_digestibility",$B$3,"ingredient",$J3)*36.2+Q3*GETPIVOTDATA("Sum of carb",$B$3,"ingredient",$J3)*GETPIVOTDATA("Sum of mean_carb_digestibility",$B$3,"ingredient",$J3)*17.2</f>
         <v>0</v>
       </c>
@@ -5356,7 +5348,7 @@
         <f>M3/SUM(M$2:M$39)</f>
         <v>2.1571331147847459E-2</v>
       </c>
-      <c r="U3" s="19">
+      <c r="U3" s="18">
         <f t="shared" ref="U3:U38" si="3">T3*GETPIVOTDATA("Sum of protein",$B$3,"ingredient",$J3)*GETPIVOTDATA("Sum of mean_protein_digestibility",$B$3,"ingredient",$J3)*23.6+T3*GETPIVOTDATA("Sum of lipid",$B$3,"ingredient",$J3)*GETPIVOTDATA("Sum of mean_lipid_digestibility",$B$3,"ingredient",$J3)*36.2+T3*GETPIVOTDATA("Sum of carb",$B$3,"ingredient",$J3)*GETPIVOTDATA("Sum of mean_carb_digestibility",$B$3,"ingredient",$J3)*17.2</f>
         <v>0</v>
       </c>
@@ -5368,7 +5360,7 @@
         <f>O3/SUM(O$2:O$39)</f>
         <v>2.6758309066129467E-3</v>
       </c>
-      <c r="X3" s="19">
+      <c r="X3" s="18">
         <f t="shared" ref="X3:X38" si="5">W3*GETPIVOTDATA("Sum of protein",$B$3,"ingredient",$J3)*GETPIVOTDATA("Sum of mean_protein_digestibility",$B$3,"ingredient",$J3)*23.6+W3*GETPIVOTDATA("Sum of lipid",$B$3,"ingredient",$J3)*GETPIVOTDATA("Sum of mean_lipid_digestibility",$B$3,"ingredient",$J3)*36.2+W3*GETPIVOTDATA("Sum of carb",$B$3,"ingredient",$J3)*GETPIVOTDATA("Sum of mean_carb_digestibility",$B$3,"ingredient",$J3)*17.2</f>
         <v>0</v>
       </c>
@@ -5381,44 +5373,44 @@
       <c r="B4" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="14">
-        <v>0</v>
-      </c>
-      <c r="D4" s="14">
-        <v>0</v>
-      </c>
-      <c r="E4" s="14">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4">
         <v>0.95176181599999998</v>
       </c>
-      <c r="G4" s="14">
-        <v>0</v>
-      </c>
-      <c r="H4" s="14">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>0</v>
       </c>
       <c r="J4" t="s">
         <v>1</v>
       </c>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15">
-        <f t="shared" ref="L3:L38" si="7">K4*GETPIVOTDATA("Sum of protein",$B$3,"ingredient",$J4)*GETPIVOTDATA("Sum of mean_protein_digestibility",$B$3,"ingredient",$J4)*23.6+K4*GETPIVOTDATA("Sum of lipid",$B$3,"ingredient",$J4)*GETPIVOTDATA("Sum of mean_lipid_digestibility",$B$3,"ingredient",$J4)*36.2+K4*GETPIVOTDATA("Sum of carb",$B$3,"ingredient",$J4)*GETPIVOTDATA("Sum of mean_carb_digestibility",$B$3,"ingredient",$J4)*17.2</f>
-        <v>0</v>
-      </c>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15">
-        <f t="shared" ref="N3:N38" si="8">M4*GETPIVOTDATA("Sum of protein",$B$3,"ingredient",$J4)*GETPIVOTDATA("Sum of mean_protein_digestibility",$B$3,"ingredient",$J4)*23.6+M4*GETPIVOTDATA("Sum of lipid",$B$3,"ingredient",$J4)*GETPIVOTDATA("Sum of mean_lipid_digestibility",$B$3,"ingredient",$J4)*36.2+M4*GETPIVOTDATA("Sum of carb",$B$3,"ingredient",$J4)*GETPIVOTDATA("Sum of mean_carb_digestibility",$B$3,"ingredient",$J4)*17.2</f>
-        <v>0</v>
-      </c>
-      <c r="O4" s="15"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L38" si="7">K4*GETPIVOTDATA("Sum of protein",$B$3,"ingredient",$J4)*GETPIVOTDATA("Sum of mean_protein_digestibility",$B$3,"ingredient",$J4)*23.6+K4*GETPIVOTDATA("Sum of lipid",$B$3,"ingredient",$J4)*GETPIVOTDATA("Sum of mean_lipid_digestibility",$B$3,"ingredient",$J4)*36.2+K4*GETPIVOTDATA("Sum of carb",$B$3,"ingredient",$J4)*GETPIVOTDATA("Sum of mean_carb_digestibility",$B$3,"ingredient",$J4)*17.2</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14">
+        <f t="shared" ref="N4:N38" si="8">M4*GETPIVOTDATA("Sum of protein",$B$3,"ingredient",$J4)*GETPIVOTDATA("Sum of mean_protein_digestibility",$B$3,"ingredient",$J4)*23.6+M4*GETPIVOTDATA("Sum of lipid",$B$3,"ingredient",$J4)*GETPIVOTDATA("Sum of mean_lipid_digestibility",$B$3,"ingredient",$J4)*36.2+M4*GETPIVOTDATA("Sum of carb",$B$3,"ingredient",$J4)*GETPIVOTDATA("Sum of mean_carb_digestibility",$B$3,"ingredient",$J4)*17.2</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="14"/>
       <c r="P4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q4" s="8"/>
-      <c r="R4" s="19">
+      <c r="R4" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5427,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="T4" s="8"/>
-      <c r="U4" s="19">
+      <c r="U4" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5436,7 +5428,7 @@
         <v>0</v>
       </c>
       <c r="W4" s="8"/>
-      <c r="X4" s="19">
+      <c r="X4" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -5449,44 +5441,44 @@
       <c r="B5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="14">
-        <v>0</v>
-      </c>
-      <c r="D5" s="14">
-        <v>0</v>
-      </c>
-      <c r="E5" s="14">
-        <v>0</v>
-      </c>
-      <c r="F5" s="14">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14">
-        <v>0</v>
-      </c>
-      <c r="H5" s="14">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>0</v>
       </c>
       <c r="J5" t="s">
         <v>2</v>
       </c>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15">
+      <c r="K5" s="14"/>
+      <c r="L5" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15">
+      <c r="M5" s="14"/>
+      <c r="N5" s="14">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O5" s="15"/>
+      <c r="O5" s="14"/>
       <c r="P5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q5" s="8"/>
-      <c r="R5" s="19">
+      <c r="R5" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5495,7 +5487,7 @@
         <v>0</v>
       </c>
       <c r="T5" s="8"/>
-      <c r="U5" s="19">
+      <c r="U5" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5504,7 +5496,7 @@
         <v>0</v>
       </c>
       <c r="W5" s="8"/>
-      <c r="X5" s="19">
+      <c r="X5" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -5517,42 +5509,42 @@
       <c r="B6" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6">
         <v>0.53500000000000003</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6">
         <v>0.86264614774680892</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6">
         <v>0.224</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6">
         <v>0.93</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6">
         <v>0.11099999999999999</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6">
         <v>0.41000000000000003</v>
       </c>
       <c r="J6" t="s">
         <v>3</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="14">
         <v>0.23649999999999999</v>
       </c>
-      <c r="L6" s="15">
+      <c r="L6" s="14">
         <f t="shared" si="7"/>
         <v>8.1483184353207996</v>
       </c>
-      <c r="M6" s="15">
+      <c r="M6" s="14">
         <v>0.34304563152606715</v>
       </c>
-      <c r="N6" s="15">
+      <c r="N6" s="14">
         <f t="shared" si="8"/>
         <v>11.819217943002618</v>
       </c>
-      <c r="O6" s="15">
+      <c r="O6" s="14">
         <v>0.10478923099049167</v>
       </c>
       <c r="P6">
@@ -5563,7 +5555,7 @@
         <f>K6/SUM(K$2:K$39)</f>
         <v>0.23647635236476347</v>
       </c>
-      <c r="R6" s="19">
+      <c r="R6" s="18">
         <f t="shared" si="1"/>
         <v>8.1475036849523033</v>
       </c>
@@ -5575,7 +5567,7 @@
         <f>M6/SUM(M$2:M$39)</f>
         <v>0.29599803665885016</v>
       </c>
-      <c r="U6" s="19">
+      <c r="U6" s="18">
         <f t="shared" si="3"/>
         <v>10.198250566283598</v>
       </c>
@@ -5587,7 +5579,7 @@
         <f>O6/SUM(O$2:O$39)</f>
         <v>0.11215930518582433</v>
       </c>
-      <c r="X6" s="19">
+      <c r="X6" s="18">
         <f t="shared" si="5"/>
         <v>3.8643117722554936</v>
       </c>
@@ -5600,160 +5592,160 @@
       <c r="B7" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7">
         <v>0.32700000000000001</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7">
         <v>0.91108708069547573</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7">
         <v>0.13</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7">
         <v>0.93</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7">
         <v>0.46672719298245613</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7">
         <v>0.68600000000000005</v>
       </c>
       <c r="J7" t="s">
         <v>4</v>
       </c>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
       <c r="Q7" s="8"/>
-      <c r="R7" s="19"/>
+      <c r="R7" s="18"/>
       <c r="S7" s="8"/>
       <c r="T7" s="8"/>
-      <c r="U7" s="19"/>
+      <c r="U7" s="18"/>
       <c r="V7" s="8"/>
       <c r="W7" s="8"/>
-      <c r="X7" s="19"/>
+      <c r="X7" s="18"/>
       <c r="Y7" s="8"/>
     </row>
     <row r="8" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="14">
-        <v>0</v>
-      </c>
-      <c r="D8" s="14">
-        <v>0</v>
-      </c>
-      <c r="E8" s="14">
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>1</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8">
         <v>0.95176181599999998</v>
       </c>
-      <c r="G8" s="14">
-        <v>0</v>
-      </c>
-      <c r="H8" s="14">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>0</v>
       </c>
       <c r="J8" t="s">
         <v>5</v>
       </c>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
       <c r="Q8" s="8"/>
-      <c r="R8" s="19"/>
+      <c r="R8" s="18"/>
       <c r="S8" s="8"/>
       <c r="T8" s="8"/>
-      <c r="U8" s="19"/>
+      <c r="U8" s="18"/>
       <c r="V8" s="8"/>
       <c r="W8" s="8"/>
-      <c r="X8" s="19"/>
+      <c r="X8" s="18"/>
       <c r="Y8" s="8"/>
     </row>
     <row r="9" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9">
         <v>0.86849038461538397</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9">
         <v>0.86596964644311503</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9">
         <v>6.7799419E-2</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9">
         <v>0.93708838073277401</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9">
         <v>1.3710196384616014E-2</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9">
         <v>0.78</v>
       </c>
       <c r="J9" t="s">
         <v>6</v>
       </c>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
       <c r="Q9" s="8"/>
-      <c r="R9" s="19"/>
+      <c r="R9" s="18"/>
       <c r="S9" s="8"/>
       <c r="T9" s="8"/>
-      <c r="U9" s="19"/>
+      <c r="U9" s="18"/>
       <c r="V9" s="8"/>
       <c r="W9" s="8"/>
-      <c r="X9" s="19"/>
+      <c r="X9" s="18"/>
       <c r="Y9" s="8"/>
     </row>
     <row r="10" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10">
         <v>0.73424999999999996</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10">
         <v>0.87984013184420995</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10">
         <v>0.95670948993092597</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10">
         <v>4.3750000000000067E-2</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10">
         <v>0.83299999999999996</v>
       </c>
       <c r="J10" t="s">
         <v>7</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="14">
         <v>2.6599999999999999E-2</v>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="14">
         <f>K10*GETPIVOTDATA("Sum of protein",$B$3,"ingredient",$J10)*GETPIVOTDATA("Sum of mean_protein_digestibility",$B$3,"ingredient",$J10)*23.6+K10*GETPIVOTDATA("Sum of lipid",$B$3,"ingredient",$J10)*GETPIVOTDATA("Sum of mean_lipid_digestibility",$B$3,"ingredient",$J10)*36.2+K10*GETPIVOTDATA("Sum of carb",$B$3,"ingredient",$J10)*GETPIVOTDATA("Sum of mean_carb_digestibility",$B$3,"ingredient",$J10)*17.2</f>
         <v>0.5382006055177021</v>
       </c>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15">
+      <c r="M10" s="14"/>
+      <c r="N10" s="14">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O10" s="15">
+      <c r="O10" s="14">
         <v>1.7100000000000001E-2</v>
       </c>
       <c r="P10">
@@ -5764,7 +5756,7 @@
         <f>K10/SUM(K$2:K$39)</f>
         <v>2.6597340265973397E-2</v>
       </c>
-      <c r="R10" s="19">
+      <c r="R10" s="18">
         <f t="shared" si="1"/>
         <v>0.53814679083861816</v>
       </c>
@@ -5773,7 +5765,7 @@
         <v>2.0003495531150012E-2</v>
       </c>
       <c r="T10" s="8"/>
-      <c r="U10" s="19">
+      <c r="U10" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5785,7 +5777,7 @@
         <f>O10/SUM(O$2:O$39)</f>
         <v>1.8302683401232554E-2</v>
       </c>
-      <c r="X10" s="19">
+      <c r="X10" s="18">
         <f t="shared" si="5"/>
         <v>0.37032012365196071</v>
       </c>
@@ -5798,42 +5790,42 @@
       <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11">
         <v>0.73424999999999996</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11">
         <v>0.87984013184420995</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11">
         <v>0.95670948993092597</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11">
         <v>4.3750000000000067E-2</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11">
         <v>0.81700000000000006</v>
       </c>
       <c r="J11" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="14">
         <v>0.22499999999999998</v>
       </c>
-      <c r="L11" s="15">
+      <c r="L11" s="14">
         <f t="shared" si="7"/>
         <v>4.2181865077685581</v>
       </c>
-      <c r="M11" s="15">
+      <c r="M11" s="14">
         <v>4.2187499999999996E-2</v>
       </c>
-      <c r="N11" s="15">
+      <c r="N11" s="14">
         <f t="shared" si="8"/>
         <v>0.7909099702066047</v>
       </c>
-      <c r="O11" s="15">
+      <c r="O11" s="14">
         <v>4.2187499999999996E-2</v>
       </c>
       <c r="P11">
@@ -5844,7 +5836,7 @@
         <f>K11/SUM(K$2:K$39)</f>
         <v>0.22497750224977495</v>
       </c>
-      <c r="R11" s="19">
+      <c r="R11" s="18">
         <f t="shared" si="1"/>
         <v>4.2177647312954285</v>
       </c>
@@ -5856,7 +5848,7 @@
         <f>M11/SUM(M$2:M$39)</f>
         <v>3.640162131199258E-2</v>
       </c>
-      <c r="U11" s="19">
+      <c r="U11" s="18">
         <f t="shared" si="3"/>
         <v>0.68243923501843351</v>
       </c>
@@ -5868,7 +5860,7 @@
         <f>O11/SUM(O$2:O$39)</f>
         <v>4.5154646549093472E-2</v>
       </c>
-      <c r="X11" s="19">
+      <c r="X11" s="18">
         <f t="shared" si="5"/>
         <v>0.84653653705086307</v>
       </c>
@@ -5881,42 +5873,42 @@
       <c r="B12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="14">
-        <v>0</v>
-      </c>
-      <c r="D12" s="14">
-        <v>0</v>
-      </c>
-      <c r="E12" s="14">
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
         <v>1</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12">
         <v>0.95670948993092597</v>
       </c>
-      <c r="G12" s="14">
-        <v>0</v>
-      </c>
-      <c r="H12" s="14">
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <v>0</v>
       </c>
       <c r="J12" t="s">
         <v>9</v>
       </c>
-      <c r="K12" s="15">
+      <c r="K12" s="14">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="L12" s="15">
+      <c r="L12" s="14">
         <f t="shared" si="7"/>
         <v>1.4051591692561862</v>
       </c>
-      <c r="M12" s="15">
+      <c r="M12" s="14">
         <v>1.4062499999999999E-2</v>
       </c>
-      <c r="N12" s="15">
+      <c r="N12" s="14">
         <f t="shared" si="8"/>
         <v>0.26346734423553492</v>
       </c>
-      <c r="O12" s="15">
+      <c r="O12" s="14">
         <v>1.4062499999999999E-2</v>
       </c>
       <c r="P12">
@@ -5927,7 +5919,7 @@
         <f>K12/SUM(K$2:K$39)</f>
         <v>7.4992500749924987E-2</v>
       </c>
-      <c r="R12" s="19">
+      <c r="R12" s="18">
         <f t="shared" si="1"/>
         <v>1.4050186673894471</v>
       </c>
@@ -5939,7 +5931,7 @@
         <f>M12/SUM(M$2:M$39)</f>
         <v>1.2133873770664194E-2</v>
       </c>
-      <c r="U12" s="19">
+      <c r="U12" s="18">
         <f t="shared" si="3"/>
         <v>0.2273336531659457</v>
       </c>
@@ -5951,7 +5943,7 @@
         <f>O12/SUM(O$2:O$39)</f>
         <v>1.5051548849697824E-2</v>
       </c>
-      <c r="X12" s="19">
+      <c r="X12" s="18">
         <f t="shared" si="5"/>
         <v>0.28199762503547071</v>
       </c>
@@ -5964,42 +5956,42 @@
       <c r="B13" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14">
-        <v>0</v>
-      </c>
-      <c r="D13" s="14">
-        <v>0</v>
-      </c>
-      <c r="E13" s="14">
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
         <v>1</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13">
         <v>0.95670948993092597</v>
       </c>
-      <c r="G13" s="14">
-        <v>0</v>
-      </c>
-      <c r="H13" s="14">
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>0</v>
       </c>
       <c r="J13" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="15">
+      <c r="K13" s="14">
         <v>5.7675000000000004E-2</v>
       </c>
-      <c r="L13" s="15">
+      <c r="L13" s="14">
         <f t="shared" si="7"/>
         <v>1.997451557909935</v>
       </c>
-      <c r="M13" s="15">
+      <c r="M13" s="14">
         <v>3.4050000000000004E-2</v>
       </c>
-      <c r="N13" s="15">
+      <c r="N13" s="14">
         <f t="shared" si="8"/>
         <v>1.1792496843837588</v>
       </c>
-      <c r="O13" s="15">
+      <c r="O13" s="14">
         <v>4.5900000000000003E-2</v>
       </c>
       <c r="P13">
@@ -6010,7 +6002,7 @@
         <f>K13/SUM(K$2:K$39)</f>
         <v>5.7669233076692319E-2</v>
       </c>
-      <c r="R13" s="19">
+      <c r="R13" s="18">
         <f t="shared" si="1"/>
         <v>1.997251832726662</v>
       </c>
@@ -6022,7 +6014,7 @@
         <f>M13/SUM(M$2:M$39)</f>
         <v>2.9380153023368241E-2</v>
       </c>
-      <c r="U13" s="19">
+      <c r="U13" s="18">
         <f t="shared" si="3"/>
         <v>1.0175194179134666</v>
       </c>
@@ -6034,7 +6026,7 @@
         <f>O13/SUM(O$2:O$39)</f>
         <v>4.9128255445413702E-2</v>
       </c>
-      <c r="X13" s="19">
+      <c r="X13" s="18">
         <f t="shared" si="5"/>
         <v>1.7014531491432829</v>
       </c>
@@ -6047,42 +6039,42 @@
       <c r="B14" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14">
         <v>0.42</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14">
         <v>0.63000000000000012</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14">
         <v>0.95176181599999998</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14">
         <v>0.46899999999999997</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14">
         <v>0.71</v>
       </c>
       <c r="J14" t="s">
         <v>11</v>
       </c>
-      <c r="K14" s="15">
+      <c r="K14" s="14">
         <v>1.9225000000000003E-2</v>
       </c>
-      <c r="L14" s="15">
+      <c r="L14" s="14">
         <f t="shared" si="7"/>
         <v>0.66581718596997841</v>
       </c>
-      <c r="M14" s="15">
+      <c r="M14" s="14">
         <v>1.1350000000000001E-2</v>
       </c>
-      <c r="N14" s="15">
+      <c r="N14" s="14">
         <f t="shared" si="8"/>
         <v>0.39308322812791963</v>
       </c>
-      <c r="O14" s="15">
+      <c r="O14" s="14">
         <v>1.5300000000000001E-2</v>
       </c>
       <c r="P14">
@@ -6093,7 +6085,7 @@
         <f>K14/SUM(K$2:K$39)</f>
         <v>1.9223077692230774E-2</v>
       </c>
-      <c r="R14" s="19">
+      <c r="R14" s="18">
         <f t="shared" si="1"/>
         <v>0.66575061090888732</v>
       </c>
@@ -6105,7 +6097,7 @@
         <f>M14/SUM(M$2:M$39)</f>
         <v>9.7933843411227468E-3</v>
       </c>
-      <c r="U14" s="19">
+      <c r="U14" s="18">
         <f t="shared" si="3"/>
         <v>0.33917313930448884</v>
       </c>
@@ -6117,7 +6109,7 @@
         <f>O14/SUM(O$2:O$39)</f>
         <v>1.6376085148471234E-2</v>
       </c>
-      <c r="X14" s="19">
+      <c r="X14" s="18">
         <f t="shared" si="5"/>
         <v>0.56715104971442765</v>
       </c>
@@ -6130,46 +6122,46 @@
       <c r="B15" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15">
         <v>0.93</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15">
         <v>0.622</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15">
         <v>0.95176181599999998</v>
       </c>
-      <c r="G15" s="14">
-        <v>0</v>
-      </c>
-      <c r="H15" s="14">
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>0.60399999999999998</v>
       </c>
       <c r="J15" t="s">
         <v>12</v>
       </c>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15">
+      <c r="K15" s="14"/>
+      <c r="L15" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M15" s="15">
+      <c r="M15" s="14">
         <v>0.17</v>
       </c>
-      <c r="N15" s="15">
+      <c r="N15" s="14">
         <f t="shared" si="8"/>
         <v>2.3456664974301922</v>
       </c>
-      <c r="O15" s="15"/>
+      <c r="O15" s="14"/>
       <c r="P15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q15" s="8"/>
-      <c r="R15" s="19">
+      <c r="R15" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6181,7 +6173,7 @@
         <f>M15/SUM(M$2:M$39)</f>
         <v>0.14668505180536273</v>
       </c>
-      <c r="U15" s="19">
+      <c r="U15" s="18">
         <f t="shared" si="3"/>
         <v>2.0239659511391261</v>
       </c>
@@ -6190,7 +6182,7 @@
         <v>3.8812864707698985E-2</v>
       </c>
       <c r="W15" s="8"/>
-      <c r="X15" s="19">
+      <c r="X15" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -6203,78 +6195,78 @@
       <c r="B16" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16">
         <v>0.55099999999999993</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16">
         <v>0.877686516894431</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16">
         <v>0.2692252</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16">
         <v>0.95114829052565797</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16">
         <v>4.08748000000001E-2</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16">
         <v>0.59399999999999997</v>
       </c>
       <c r="J16" t="s">
         <v>13</v>
       </c>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
       <c r="Q16" s="8"/>
-      <c r="R16" s="19"/>
+      <c r="R16" s="18"/>
       <c r="S16" s="8"/>
       <c r="T16" s="8"/>
-      <c r="U16" s="19"/>
+      <c r="U16" s="18"/>
       <c r="V16" s="8"/>
       <c r="W16" s="8"/>
-      <c r="X16" s="19"/>
+      <c r="X16" s="18"/>
       <c r="Y16" s="8"/>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17">
         <v>0.53783333333333327</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17">
         <v>0.83030542718534806</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17">
         <v>0.13249432999999999</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17">
         <v>0.93189462648181998</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G17">
         <v>2.4672336666666794E-2</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17">
         <v>0.68700000000000006</v>
       </c>
       <c r="J17" t="s">
         <v>49</v>
       </c>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15">
+      <c r="K17" s="14"/>
+      <c r="L17" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15">
+      <c r="M17" s="14"/>
+      <c r="N17" s="14">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O17" s="15">
+      <c r="O17" s="14">
         <v>1.83E-2</v>
       </c>
       <c r="P17">
@@ -6282,7 +6274,7 @@
         <v>0.29396059408391528</v>
       </c>
       <c r="Q17" s="8"/>
-      <c r="R17" s="19">
+      <c r="R17" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6291,7 +6283,7 @@
         <v>0</v>
       </c>
       <c r="T17" s="8"/>
-      <c r="U17" s="19">
+      <c r="U17" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6303,7 +6295,7 @@
         <f>O17/SUM(O$2:O$39)</f>
         <v>1.9587082236406768E-2</v>
       </c>
-      <c r="X17" s="19">
+      <c r="X17" s="18">
         <f t="shared" si="5"/>
         <v>0.31463553719041731</v>
       </c>
@@ -6314,44 +6306,44 @@
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="14">
+        <v>66</v>
+      </c>
+      <c r="C18">
         <v>0.56188888888888899</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18">
         <v>0.81159790994043479</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18">
         <v>0.93</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18">
         <v>0.23711111111111105</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18">
         <v>0.68700000000000006</v>
       </c>
       <c r="J18" t="s">
         <v>14</v>
       </c>
-      <c r="K18" s="15">
+      <c r="K18" s="14">
         <v>0.1</v>
       </c>
-      <c r="L18" s="15">
+      <c r="L18" s="14">
         <f t="shared" si="7"/>
         <v>2.110053986034913</v>
       </c>
-      <c r="M18" s="15">
+      <c r="M18" s="14">
         <v>1.8749999999999999E-2</v>
       </c>
-      <c r="N18" s="15">
+      <c r="N18" s="14">
         <f t="shared" si="8"/>
         <v>0.39563512238154619</v>
       </c>
-      <c r="O18" s="15">
+      <c r="O18" s="14">
         <v>1.8749999999999999E-2</v>
       </c>
       <c r="P18">
@@ -6362,7 +6354,7 @@
         <f>K18/SUM(K$2:K$39)</f>
         <v>9.9990000999899992E-2</v>
       </c>
-      <c r="R18" s="19">
+      <c r="R18" s="18">
         <f t="shared" si="1"/>
         <v>2.1098430017347396</v>
       </c>
@@ -6374,7 +6366,7 @@
         <f>M18/SUM(M$2:M$39)</f>
         <v>1.6178498360885592E-2</v>
       </c>
-      <c r="U18" s="19">
+      <c r="U18" s="18">
         <f t="shared" si="3"/>
         <v>0.34137504954445952</v>
       </c>
@@ -6386,7 +6378,7 @@
         <f>O18/SUM(O$2:O$39)</f>
         <v>2.00687317995971E-2</v>
       </c>
-      <c r="X18" s="19">
+      <c r="X18" s="18">
         <f t="shared" si="5"/>
         <v>0.42346107528405474</v>
       </c>
@@ -6399,86 +6391,86 @@
       <c r="B19" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="14">
-        <v>0</v>
-      </c>
-      <c r="D19" s="14">
-        <v>0</v>
-      </c>
-      <c r="E19" s="14">
-        <v>0</v>
-      </c>
-      <c r="F19" s="14">
-        <v>0</v>
-      </c>
-      <c r="G19" s="14">
-        <v>0</v>
-      </c>
-      <c r="H19" s="14">
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
         <v>0</v>
       </c>
       <c r="J19" t="s">
         <v>15</v>
       </c>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
       <c r="Q19" s="8"/>
-      <c r="R19" s="19"/>
+      <c r="R19" s="18"/>
       <c r="S19" s="8"/>
       <c r="T19" s="8"/>
-      <c r="U19" s="19"/>
+      <c r="U19" s="18"/>
       <c r="V19" s="8"/>
       <c r="W19" s="8"/>
-      <c r="X19" s="19"/>
+      <c r="X19" s="18"/>
       <c r="Y19" s="8"/>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20">
         <v>0.62166666666666659</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20">
         <v>0.78638081783306735</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20">
         <v>0.122</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20">
         <v>0.93</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G20">
         <v>0.14233333333333342</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20">
         <v>0.68900000000000006</v>
       </c>
       <c r="J20" t="s">
-        <v>133</v>
-      </c>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15">
+        <v>130</v>
+      </c>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M20" s="15">
+      <c r="M20" s="14">
         <v>1.6E-2</v>
       </c>
-      <c r="N20" s="15">
+      <c r="N20" s="14">
         <f t="shared" si="8"/>
         <v>0.30791562569726894</v>
       </c>
-      <c r="O20" s="15"/>
+      <c r="O20" s="14"/>
       <c r="P20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q20" s="8"/>
-      <c r="R20" s="19">
+      <c r="R20" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6490,7 +6482,7 @@
         <f>M20/SUM(M$2:M$39)</f>
         <v>1.3805651934622375E-2</v>
       </c>
-      <c r="U20" s="19">
+      <c r="U20" s="18">
         <f t="shared" si="3"/>
         <v>0.26568599710049745</v>
       </c>
@@ -6499,7 +6491,7 @@
         <v>5.14009340727733E-3</v>
       </c>
       <c r="W20" s="8"/>
-      <c r="X20" s="19">
+      <c r="X20" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -6512,38 +6504,38 @@
       <c r="B21" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C21">
         <v>0.84</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21">
         <v>0.88</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21">
         <v>0.05</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21">
         <v>0.95176181599999998</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G21">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21">
         <v>0.77</v>
       </c>
       <c r="J21" t="s">
         <v>16</v>
       </c>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15">
+      <c r="K21" s="14"/>
+      <c r="L21" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M21" s="15"/>
-      <c r="N21" s="15">
+      <c r="M21" s="14"/>
+      <c r="N21" s="14">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O21" s="15">
+      <c r="O21" s="14">
         <v>0.1</v>
       </c>
       <c r="P21">
@@ -6551,7 +6543,7 @@
         <v>1.530013557968172</v>
       </c>
       <c r="Q21" s="8"/>
-      <c r="R21" s="19">
+      <c r="R21" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6560,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="T21" s="8"/>
-      <c r="U21" s="19">
+      <c r="U21" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6572,7 +6564,7 @@
         <f>O21/SUM(O$2:O$39)</f>
         <v>0.10703323626451787</v>
       </c>
-      <c r="X21" s="19">
+      <c r="X21" s="18">
         <f t="shared" si="5"/>
         <v>1.6376230263792295</v>
       </c>
@@ -6585,36 +6577,36 @@
       <c r="B22" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22">
         <v>0.72292857142857125</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22">
         <v>0.86610883281803497</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22">
         <v>0.11689690000000001</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22">
         <v>0.94897384021576103</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G22">
         <v>5.4174528571428793E-2</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22">
         <v>0.68899999999999995</v>
       </c>
       <c r="J22" t="s">
         <v>17</v>
       </c>
-      <c r="K22" s="17">
+      <c r="K22" s="16">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="L22" s="15"/>
-      <c r="M22" s="17">
+      <c r="L22" s="14"/>
+      <c r="M22" s="16">
         <v>0.02</v>
       </c>
-      <c r="N22" s="15"/>
-      <c r="O22" s="17">
+      <c r="N22" s="14"/>
+      <c r="O22" s="16">
         <v>1.12E-2</v>
       </c>
       <c r="P22">
@@ -6625,7 +6617,7 @@
         <f>K22/SUM(K$2:K$39)</f>
         <v>1.0998900109988998E-2</v>
       </c>
-      <c r="R22" s="19">
+      <c r="R22" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6637,7 +6629,7 @@
         <f>M22/SUM(M$2:M$39)</f>
         <v>1.7257064918277967E-2</v>
       </c>
-      <c r="U22" s="19">
+      <c r="U22" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6649,7 +6641,7 @@
         <f>O22/SUM(O$2:O$39)</f>
         <v>1.1987722461626001E-2</v>
       </c>
-      <c r="X22" s="19">
+      <c r="X22" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -6662,44 +6654,44 @@
       <c r="B23" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="14">
-        <v>0</v>
-      </c>
-      <c r="D23" s="14">
-        <v>0</v>
-      </c>
-      <c r="E23" s="14">
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
         <v>1</v>
       </c>
-      <c r="F23" s="14">
+      <c r="F23">
         <v>0.96578520322974404</v>
       </c>
-      <c r="G23" s="14">
-        <v>0</v>
-      </c>
-      <c r="H23" s="14">
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
         <v>0</v>
       </c>
       <c r="J23" t="s">
         <v>18</v>
       </c>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15">
+      <c r="K23" s="14"/>
+      <c r="L23" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M23" s="15"/>
-      <c r="N23" s="15">
+      <c r="M23" s="14"/>
+      <c r="N23" s="14">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O23" s="15"/>
+      <c r="O23" s="14"/>
       <c r="P23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q23" s="8"/>
-      <c r="R23" s="19">
+      <c r="R23" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6708,7 +6700,7 @@
         <v>0</v>
       </c>
       <c r="T23" s="8"/>
-      <c r="U23" s="19">
+      <c r="U23" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6717,7 +6709,7 @@
         <v>0</v>
       </c>
       <c r="W23" s="8"/>
-      <c r="X23" s="19">
+      <c r="X23" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -6730,86 +6722,86 @@
       <c r="B24" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C24">
         <v>0.81849999999999989</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24">
         <v>0.88381879361953897</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24">
         <v>0.14486250000000001</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F24">
         <v>0.96578520322974404</v>
       </c>
-      <c r="G24" s="14">
+      <c r="G24">
         <v>6.6375000000000739E-3</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H24">
         <v>0.88000000000000012</v>
       </c>
       <c r="J24" t="s">
         <v>19</v>
       </c>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="15"/>
-      <c r="O24" s="15"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
       <c r="Q24" s="8"/>
-      <c r="R24" s="19"/>
+      <c r="R24" s="18"/>
       <c r="S24" s="8"/>
       <c r="T24" s="8"/>
-      <c r="U24" s="19"/>
+      <c r="U24" s="18"/>
       <c r="V24" s="8"/>
       <c r="W24" s="8"/>
-      <c r="X24" s="19"/>
+      <c r="X24" s="18"/>
       <c r="Y24" s="8"/>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C25">
         <v>0.75900000000000001</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25">
         <v>0.94144621422710895</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E25">
         <v>0.10100000000000001</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F25">
         <v>0.93</v>
       </c>
-      <c r="G25" s="14">
-        <v>0</v>
-      </c>
-      <c r="H25" s="14">
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
         <v>0.68000000000000016</v>
       </c>
       <c r="J25" t="s">
         <v>20</v>
       </c>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15">
+      <c r="K25" s="14"/>
+      <c r="L25" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M25" s="15">
+      <c r="M25" s="14">
         <v>2.69E-2</v>
       </c>
-      <c r="N25" s="15">
+      <c r="N25" s="14">
         <f t="shared" si="8"/>
         <v>0.54055251105922397</v>
       </c>
-      <c r="O25" s="15"/>
+      <c r="O25" s="14"/>
       <c r="P25">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q25" s="8"/>
-      <c r="R25" s="19">
+      <c r="R25" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6821,7 +6813,7 @@
         <f>M25/SUM(M$2:M$39)</f>
         <v>2.3210752315083866E-2</v>
       </c>
-      <c r="U25" s="19">
+      <c r="U25" s="18">
         <f t="shared" si="3"/>
         <v>0.4664174887543599</v>
       </c>
@@ -6830,7 +6822,7 @@
         <v>1.7157388111309995E-2</v>
       </c>
       <c r="W25" s="8"/>
-      <c r="X25" s="19">
+      <c r="X25" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -6843,40 +6835,40 @@
       <c r="B26" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C26">
         <v>0.65300000000000002</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26">
         <v>0.8937733673883973</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26">
         <v>0.02</v>
       </c>
-      <c r="F26" s="14">
+      <c r="F26">
         <v>0.93</v>
       </c>
-      <c r="G26" s="14">
+      <c r="G26">
         <v>0.2569999999999999</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H26">
         <v>0.82</v>
       </c>
       <c r="J26" t="s">
         <v>21</v>
       </c>
-      <c r="K26" s="15">
+      <c r="K26" s="14">
         <v>3.78E-2</v>
       </c>
-      <c r="L26" s="15">
+      <c r="L26" s="14">
         <f t="shared" si="7"/>
         <v>0.73462543462249041</v>
       </c>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15">
+      <c r="M26" s="14"/>
+      <c r="N26" s="14">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O26" s="15">
+      <c r="O26" s="14">
         <v>0.25</v>
       </c>
       <c r="P26">
@@ -6887,7 +6879,7 @@
         <f>K26/SUM(K$2:K$39)</f>
         <v>3.7796220377962195E-2</v>
       </c>
-      <c r="R26" s="19">
+      <c r="R26" s="18">
         <f t="shared" si="1"/>
         <v>0.73455197942454786</v>
       </c>
@@ -6896,7 +6888,7 @@
         <v>2.3665529688799706E-2</v>
       </c>
       <c r="T26" s="8"/>
-      <c r="U26" s="19">
+      <c r="U26" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6908,7 +6900,7 @@
         <f>O26/SUM(O$2:O$39)</f>
         <v>0.26758309066129465</v>
       </c>
-      <c r="X26" s="19">
+      <c r="X26" s="18">
         <f t="shared" si="5"/>
         <v>5.2003530231397574</v>
       </c>
@@ -6921,38 +6913,38 @@
       <c r="B27" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27">
         <v>0.66174999999999995</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27">
         <v>0.87600843567991205</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E27">
         <v>1.126924E-2</v>
       </c>
-      <c r="F27" s="14">
+      <c r="F27">
         <v>0.95176181599999998</v>
       </c>
-      <c r="G27" s="14">
+      <c r="G27">
         <v>0.25398076000000014</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27">
         <v>0.875</v>
       </c>
       <c r="J27" t="s">
         <v>51</v>
       </c>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15">
+      <c r="K27" s="14"/>
+      <c r="L27" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15">
+      <c r="M27" s="14"/>
+      <c r="N27" s="14">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O27" s="15">
+      <c r="O27" s="14">
         <v>0.1</v>
       </c>
       <c r="P27">
@@ -6960,7 +6952,7 @@
         <v>3.4961424356916742</v>
       </c>
       <c r="Q27" s="8"/>
-      <c r="R27" s="19">
+      <c r="R27" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6969,7 +6961,7 @@
         <v>0</v>
       </c>
       <c r="T27" s="8"/>
-      <c r="U27" s="19">
+      <c r="U27" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6981,7 +6973,7 @@
         <f>O27/SUM(O$2:O$39)</f>
         <v>0.10703323626451787</v>
       </c>
-      <c r="X27" s="19">
+      <c r="X27" s="18">
         <f t="shared" si="5"/>
         <v>3.742034393337939</v>
       </c>
@@ -6994,38 +6986,38 @@
       <c r="B28" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28">
         <v>0.13</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28">
         <v>0.9</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28">
         <v>0.02</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F28">
         <v>0.95176181599999998</v>
       </c>
-      <c r="G28" s="14">
+      <c r="G28">
         <v>0.83000000000000007</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H28">
         <v>0.8</v>
       </c>
       <c r="J28" t="s">
         <v>52</v>
       </c>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15">
+      <c r="K28" s="14"/>
+      <c r="L28" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15">
+      <c r="M28" s="14"/>
+      <c r="N28" s="14">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O28" s="15">
+      <c r="O28" s="14">
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="P28">
@@ -7033,7 +7025,7 @@
         <v>1.0006847390130766</v>
       </c>
       <c r="Q28" s="8"/>
-      <c r="R28" s="19">
+      <c r="R28" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7042,7 +7034,7 @@
         <v>0</v>
       </c>
       <c r="T28" s="8"/>
-      <c r="U28" s="19">
+      <c r="U28" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7054,7 +7046,7 @@
         <f>O28/SUM(O$2:O$39)</f>
         <v>4.8164956319033038E-2</v>
       </c>
-      <c r="X28" s="19">
+      <c r="X28" s="18">
         <f t="shared" si="5"/>
         <v>1.0710652609708402</v>
       </c>
@@ -7067,44 +7059,44 @@
       <c r="B29" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29">
         <v>0.76600000000000001</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D29">
         <v>0.89</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E29">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="F29" s="14">
+      <c r="F29">
         <v>0.95176181599999998</v>
       </c>
-      <c r="G29" s="14">
+      <c r="G29">
         <v>0.15300000000000002</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H29">
         <v>0.75</v>
       </c>
       <c r="J29" t="s">
         <v>23</v>
       </c>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15">
+      <c r="K29" s="14"/>
+      <c r="L29" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M29" s="15"/>
-      <c r="N29" s="15">
+      <c r="M29" s="14"/>
+      <c r="N29" s="14">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O29" s="15"/>
+      <c r="O29" s="14"/>
       <c r="P29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q29" s="8"/>
-      <c r="R29" s="19">
+      <c r="R29" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7113,7 +7105,7 @@
         <v>0</v>
       </c>
       <c r="T29" s="8"/>
-      <c r="U29" s="19">
+      <c r="U29" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7122,7 +7114,7 @@
         <v>0</v>
       </c>
       <c r="W29" s="8"/>
-      <c r="X29" s="19">
+      <c r="X29" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7133,46 +7125,46 @@
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B30" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C30" s="14">
+        <v>130</v>
+      </c>
+      <c r="C30">
         <v>0.41809999999999997</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30">
         <v>0.89050000000000007</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30">
         <v>0.14003333333333337</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30">
         <v>0.95176181599999998</v>
       </c>
-      <c r="G30" s="14">
+      <c r="G30">
         <v>0.41068333333333329</v>
       </c>
-      <c r="H30" s="14">
+      <c r="H30">
         <v>0.79749999999999999</v>
       </c>
       <c r="J30" t="s">
         <v>24</v>
       </c>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15">
+      <c r="K30" s="14"/>
+      <c r="L30" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M30" s="15"/>
-      <c r="N30" s="15">
+      <c r="M30" s="14"/>
+      <c r="N30" s="14">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O30" s="15"/>
+      <c r="O30" s="14"/>
       <c r="P30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q30" s="8"/>
-      <c r="R30" s="19">
+      <c r="R30" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7181,7 +7173,7 @@
         <v>0</v>
       </c>
       <c r="T30" s="8"/>
-      <c r="U30" s="19">
+      <c r="U30" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7190,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="W30" s="8"/>
-      <c r="X30" s="19">
+      <c r="X30" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7204,19 +7196,19 @@
       <c r="J31" t="s">
         <v>25</v>
       </c>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="15"/>
-      <c r="O31" s="15"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
       <c r="Q31" s="8"/>
-      <c r="R31" s="19"/>
+      <c r="R31" s="18"/>
       <c r="S31" s="8"/>
       <c r="T31" s="8"/>
-      <c r="U31" s="19"/>
+      <c r="U31" s="18"/>
       <c r="V31" s="8"/>
       <c r="W31" s="8"/>
-      <c r="X31" s="19"/>
+      <c r="X31" s="18"/>
       <c r="Y31" s="8"/>
     </row>
     <row r="32" spans="2:25" x14ac:dyDescent="0.3">
@@ -7224,25 +7216,25 @@
       <c r="J32" t="s">
         <v>26</v>
       </c>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15">
+      <c r="K32" s="14"/>
+      <c r="L32" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M32" s="15">
+      <c r="M32" s="14">
         <v>0.17</v>
       </c>
-      <c r="N32" s="15">
+      <c r="N32" s="14">
         <f t="shared" si="8"/>
         <v>3.0415660280349108</v>
       </c>
-      <c r="O32" s="15"/>
+      <c r="O32" s="14"/>
       <c r="P32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q32" s="8"/>
-      <c r="R32" s="19">
+      <c r="R32" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7254,7 +7246,7 @@
         <f>M32/SUM(M$2:M$39)</f>
         <v>0.14668505180536273</v>
       </c>
-      <c r="U32" s="19">
+      <c r="U32" s="18">
         <f t="shared" si="3"/>
         <v>2.6244251199513662</v>
       </c>
@@ -7263,7 +7255,7 @@
         <v>8.5033116577811027E-2</v>
       </c>
       <c r="W32" s="8"/>
-      <c r="X32" s="19">
+      <c r="X32" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7277,19 +7269,19 @@
       <c r="J33" t="s">
         <v>27</v>
       </c>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="15"/>
-      <c r="O33" s="15"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14"/>
       <c r="Q33" s="8"/>
-      <c r="R33" s="19"/>
+      <c r="R33" s="18"/>
       <c r="S33" s="8"/>
       <c r="T33" s="8"/>
-      <c r="U33" s="19"/>
+      <c r="U33" s="18"/>
       <c r="V33" s="8"/>
       <c r="W33" s="8"/>
-      <c r="X33" s="19"/>
+      <c r="X33" s="18"/>
       <c r="Y33" s="8"/>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.3">
@@ -7297,19 +7289,19 @@
       <c r="J34" t="s">
         <v>28</v>
       </c>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="15"/>
-      <c r="O34" s="15"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="14"/>
+      <c r="O34" s="14"/>
       <c r="Q34" s="8"/>
-      <c r="R34" s="19"/>
+      <c r="R34" s="18"/>
       <c r="S34" s="8"/>
       <c r="T34" s="8"/>
-      <c r="U34" s="19"/>
+      <c r="U34" s="18"/>
       <c r="V34" s="8"/>
       <c r="W34" s="8"/>
-      <c r="X34" s="19"/>
+      <c r="X34" s="18"/>
       <c r="Y34" s="8"/>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.3">
@@ -7317,19 +7309,19 @@
       <c r="J35" t="s">
         <v>29</v>
       </c>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="15"/>
-      <c r="O35" s="15"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="14"/>
+      <c r="O35" s="14"/>
       <c r="Q35" s="8"/>
-      <c r="R35" s="19"/>
+      <c r="R35" s="18"/>
       <c r="S35" s="8"/>
       <c r="T35" s="8"/>
-      <c r="U35" s="19"/>
+      <c r="U35" s="18"/>
       <c r="V35" s="8"/>
       <c r="W35" s="8"/>
-      <c r="X35" s="19"/>
+      <c r="X35" s="18"/>
       <c r="Y35" s="8"/>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.3">
@@ -7337,19 +7329,19 @@
       <c r="J36" t="s">
         <v>30</v>
       </c>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="15"/>
-      <c r="O36" s="15"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="14"/>
+      <c r="O36" s="14"/>
       <c r="Q36" s="8"/>
-      <c r="R36" s="19"/>
+      <c r="R36" s="18"/>
       <c r="S36" s="8"/>
       <c r="T36" s="8"/>
-      <c r="U36" s="19"/>
+      <c r="U36" s="18"/>
       <c r="V36" s="8"/>
       <c r="W36" s="8"/>
-      <c r="X36" s="19"/>
+      <c r="X36" s="18"/>
       <c r="Y36" s="8"/>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.3">
@@ -7357,21 +7349,21 @@
       <c r="J37" t="s">
         <v>31</v>
       </c>
-      <c r="K37" s="15">
+      <c r="K37" s="14">
         <v>0.2087</v>
       </c>
-      <c r="L37" s="15">
+      <c r="L37" s="14">
         <f t="shared" si="7"/>
         <v>3.103593468283421</v>
       </c>
-      <c r="M37" s="15">
+      <c r="M37" s="14">
         <v>0.12</v>
       </c>
-      <c r="N37" s="15">
+      <c r="N37" s="14">
         <f t="shared" si="8"/>
         <v>1.7845290665740801</v>
       </c>
-      <c r="O37" s="15">
+      <c r="O37" s="14">
         <v>0.1242</v>
       </c>
       <c r="P37">
@@ -7382,7 +7374,7 @@
         <f>K37/SUM(K$2:K$39)</f>
         <v>0.20867913208679129</v>
       </c>
-      <c r="R37" s="19">
+      <c r="R37" s="18">
         <f t="shared" si="1"/>
         <v>3.1032831399694238</v>
       </c>
@@ -7394,7 +7386,7 @@
         <f>M37/SUM(M$2:M$39)</f>
         <v>0.10354238950966779</v>
       </c>
-      <c r="U37" s="19">
+      <c r="U37" s="18">
         <f t="shared" si="3"/>
         <v>1.5397866975211441</v>
       </c>
@@ -7406,7 +7398,7 @@
         <f>O37/SUM(O$2:O$39)</f>
         <v>0.13293527944053118</v>
       </c>
-      <c r="X37" s="19">
+      <c r="X37" s="18">
         <f t="shared" si="5"/>
         <v>1.9768905844564637</v>
       </c>
@@ -7420,25 +7412,25 @@
       <c r="J38" t="s">
         <v>32</v>
       </c>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15">
+      <c r="K38" s="14"/>
+      <c r="L38" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M38" s="15">
+      <c r="M38" s="14">
         <v>0.1</v>
       </c>
-      <c r="N38" s="15">
+      <c r="N38" s="14">
         <f t="shared" si="8"/>
         <v>2.0612343552700798</v>
       </c>
-      <c r="O38" s="15"/>
+      <c r="O38" s="14"/>
       <c r="P38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q38" s="8"/>
-      <c r="R38" s="19">
+      <c r="R38" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7450,7 +7442,7 @@
         <f>M38/SUM(M$2:M$39)</f>
         <v>8.6285324591389836E-2</v>
       </c>
-      <c r="U38" s="19">
+      <c r="U38" s="18">
         <f t="shared" si="3"/>
         <v>1.7785427540340304</v>
       </c>
@@ -7459,7 +7451,7 @@
         <v>5.8824157186934109E-2</v>
       </c>
       <c r="W38" s="8"/>
-      <c r="X38" s="19">
+      <c r="X38" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7486,28 +7478,28 @@
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.3">
       <c r="O41" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q41" s="16">
+        <v>137</v>
+      </c>
+      <c r="Q41" s="15">
         <f>SUM(R2:R39)</f>
         <v>22.919114439240058</v>
       </c>
-      <c r="R41" s="16"/>
-      <c r="S41" s="16"/>
-      <c r="T41" s="16">
+      <c r="R41" s="15"/>
+      <c r="S41" s="15"/>
+      <c r="T41" s="15">
         <f>SUM(U2:U39)</f>
         <v>22.919994238049117</v>
       </c>
-      <c r="U41" s="16"/>
-      <c r="V41" s="16"/>
-      <c r="W41" s="16">
+      <c r="U41" s="15"/>
+      <c r="V41" s="15"/>
+      <c r="W41" s="15">
         <f>SUM(X2:X39)</f>
         <v>22.919757990851444</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="O42" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="Q42" s="12">
         <f>SUM(S2:S38)</f>
@@ -7523,14 +7515,14 @@
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="Q43" s="18">
+      <c r="Q43" s="17">
         <f>SUM(Q2:Q39)</f>
         <v>0.99999999999999978</v>
       </c>
       <c r="R43" s="12"/>
       <c r="S43" s="12"/>
       <c r="T43" s="12">
-        <f t="shared" ref="R43:W43" si="9">SUM(T2:T39)</f>
+        <f t="shared" ref="T43:W43" si="9">SUM(T2:T39)</f>
         <v>0.99999999999999978</v>
       </c>
       <c r="U43" s="12"/>
@@ -7542,50 +7534,50 @@
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C45" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G45" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>95</v>
+      </c>
+      <c r="B46" t="s">
+        <v>94</v>
+      </c>
+      <c r="C46" t="s">
+        <v>100</v>
+      </c>
+      <c r="D46" t="s">
+        <v>97</v>
+      </c>
+      <c r="E46" t="s">
         <v>98</v>
       </c>
-      <c r="B46" t="s">
+      <c r="F46" t="s">
+        <v>99</v>
+      </c>
+      <c r="G46" t="s">
+        <v>100</v>
+      </c>
+      <c r="H46" t="s">
         <v>97</v>
       </c>
-      <c r="C46" t="s">
-        <v>103</v>
-      </c>
-      <c r="D46" t="s">
-        <v>100</v>
-      </c>
-      <c r="E46" t="s">
-        <v>101</v>
-      </c>
-      <c r="F46" t="s">
-        <v>102</v>
-      </c>
-      <c r="G46" t="s">
-        <v>103</v>
-      </c>
-      <c r="H46" t="s">
-        <v>100</v>
-      </c>
       <c r="I46" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J46" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K46" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B47" t="s">
         <v>1</v>
@@ -7629,7 +7621,7 @@
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B48" t="s">
         <v>2</v>
@@ -7673,7 +7665,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B49" t="s">
         <v>7</v>
@@ -7717,7 +7709,7 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B50" t="s">
         <v>14</v>
@@ -7761,7 +7753,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B51" t="s">
         <v>16</v>
@@ -7805,10 +7797,10 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B52" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C52">
         <f t="shared" si="10"/>
@@ -7849,7 +7841,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B53" t="s">
         <v>18</v>
@@ -7893,7 +7885,7 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B54" t="s">
         <v>21</v>
@@ -7937,7 +7929,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B55" t="s">
         <v>52</v>
@@ -7981,7 +7973,7 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B56" t="s">
         <v>23</v>
@@ -8025,7 +8017,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B57" t="s">
         <v>24</v>
@@ -8069,7 +8061,7 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B58" t="s">
         <v>26</v>
@@ -8113,7 +8105,7 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B60" t="s">
         <v>47</v>
@@ -8157,7 +8149,7 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B61" t="s">
         <v>3</v>
@@ -8201,7 +8193,7 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B62" t="s">
         <v>8</v>
@@ -8245,7 +8237,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B63" t="s">
         <v>9</v>
@@ -8289,7 +8281,7 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B64" t="s">
         <v>10</v>
@@ -8333,7 +8325,7 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B65" t="s">
         <v>11</v>
@@ -8377,7 +8369,7 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B66" t="s">
         <v>12</v>
@@ -8421,7 +8413,7 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B67" t="s">
         <v>49</v>
@@ -8465,7 +8457,7 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B68" t="s">
         <v>50</v>
@@ -8509,7 +8501,7 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B69" t="s">
         <v>20</v>
@@ -8553,7 +8545,7 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B70" t="s">
         <v>51</v>
@@ -8597,7 +8589,7 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B71" t="s">
         <v>31</v>
@@ -8641,7 +8633,7 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B72" t="s">
         <v>32</v>
@@ -8685,7 +8677,7 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B73" t="s">
         <v>48</v>
@@ -8729,7 +8721,7 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B74" t="s">
         <v>17</v>
@@ -8779,7 +8771,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA17DA89-E85F-4597-B94B-473613FC79D7}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:D43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8793,51 +8784,50 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>47</v>
       </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>48</v>
       </c>
-      <c r="B3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
         <v>60</v>
@@ -8845,390 +8835,386 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
+      </c>
+      <c r="C12" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" t="s">
-        <v>86</v>
+        <v>68</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4" t="s">
         <v>68</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>12</v>
       </c>
-      <c r="B16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>68</v>
+      </c>
+      <c r="C17" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>14</v>
       </c>
-      <c r="B19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>16</v>
       </c>
-      <c r="B22" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>69</v>
-      </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>17</v>
       </c>
-      <c r="B24" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="B25" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>18</v>
       </c>
-      <c r="B25" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>19</v>
-      </c>
       <c r="B26" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>52</v>
       </c>
-      <c r="B30" t="s">
-        <v>71</v>
-      </c>
-      <c r="C30" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>22</v>
       </c>
-      <c r="B31" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>23</v>
       </c>
-      <c r="B32" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="B33" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>24</v>
       </c>
-      <c r="B33" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>25</v>
-      </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>26</v>
       </c>
-      <c r="B35" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" s="1" t="s">
+      <c r="B36" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>27</v>
       </c>
-      <c r="B36" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="1" t="s">
+      <c r="B37" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D37" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>28</v>
       </c>
-      <c r="B37" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="1" t="s">
+      <c r="B38" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>29</v>
       </c>
-      <c r="B38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C38" s="1" t="s">
+      <c r="B39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>30</v>
-      </c>
-      <c r="B39" t="s">
-        <v>72</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>69</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>32</v>
       </c>
-      <c r="B41" t="s">
-        <v>71</v>
-      </c>
-      <c r="C41" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="B42" t="s">
+        <v>68</v>
+      </c>
+      <c r="C42" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>33</v>
       </c>
-      <c r="B42" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3" t="s">
-        <v>66</v>
+      <c r="B43" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D43" xr:uid="{BA17DA89-E85F-4597-B94B-473613FC79D7}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="T"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D43">
       <sortCondition ref="A1:A43"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="C39" r:id="rId1" display="https://www.feedipedia.org/node/527" xr:uid="{9D796F16-2A55-41F2-B066-40FB62D78DA3}"/>
-    <hyperlink ref="C38" r:id="rId2" display="https://www.feedipedia.org/node/12806" xr:uid="{0D3F6475-3F7E-4230-BF5D-1B1A9D67D318}"/>
-    <hyperlink ref="C37" r:id="rId3" display="https://www.feedipedia.org/node/12663" xr:uid="{850085C4-4E6D-4C43-806A-BA1985D7CE16}"/>
-    <hyperlink ref="C36" r:id="rId4" display="https://www.feedipedia.org/node/67" xr:uid="{679D6967-9E8A-4CC2-9A7F-D066F495C0D1}"/>
-    <hyperlink ref="C35" r:id="rId5" display="https://www.feedipedia.org/node/11683" xr:uid="{D8DFDFB1-7112-4CB0-892D-35C58DF37EC7}"/>
-    <hyperlink ref="C18" r:id="rId6" display="https://www.feedipedia.org/node/11574" xr:uid="{9C3D8932-B7C3-4F23-B5AF-0CCF9B1CF004}"/>
-    <hyperlink ref="C11" r:id="rId7" xr:uid="{731F2494-EBD0-4189-90DD-144FE15605E0}"/>
-    <hyperlink ref="C12" r:id="rId8" display="https://www.feedipedia.org/node/11687" xr:uid="{0ABC761E-265E-4D42-A75F-0D6FCBFE9A86}"/>
+    <hyperlink ref="C40" r:id="rId1" display="https://www.feedipedia.org/node/527" xr:uid="{9D796F16-2A55-41F2-B066-40FB62D78DA3}"/>
+    <hyperlink ref="C39" r:id="rId2" display="https://www.feedipedia.org/node/12806" xr:uid="{0D3F6475-3F7E-4230-BF5D-1B1A9D67D318}"/>
+    <hyperlink ref="C38" r:id="rId3" display="https://www.feedipedia.org/node/12663" xr:uid="{850085C4-4E6D-4C43-806A-BA1985D7CE16}"/>
+    <hyperlink ref="C37" r:id="rId4" display="https://www.feedipedia.org/node/67" xr:uid="{679D6967-9E8A-4CC2-9A7F-D066F495C0D1}"/>
+    <hyperlink ref="C36" r:id="rId5" display="https://www.feedipedia.org/node/11683" xr:uid="{D8DFDFB1-7112-4CB0-892D-35C58DF37EC7}"/>
+    <hyperlink ref="C19" r:id="rId6" display="https://www.feedipedia.org/node/11574" xr:uid="{9C3D8932-B7C3-4F23-B5AF-0CCF9B1CF004}"/>
+    <hyperlink ref="C13" r:id="rId7" xr:uid="{731F2494-EBD0-4189-90DD-144FE15605E0}"/>
+    <hyperlink ref="C14" r:id="rId8" display="https://www.feedipedia.org/node/11687" xr:uid="{0ABC761E-265E-4D42-A75F-0D6FCBFE9A86}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
